--- a/InputData/indst/SYIEUEFbIPaF/Start Year Indst Eqpt Unit E Factor by Indst Proc and Fuel.xlsx
+++ b/InputData/indst/SYIEUEFbIPaF/Start Year Indst Eqpt Unit E Factor by Indst Proc and Fuel.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\indst\SYIEUEFbIPaF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B79DBB7D-49B8-4EDE-BEDA-34D150F9ED5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C259C5F-CC8F-477A-B3EF-1E65F837C8F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="838" xr2:uid="{910269CE-FD31-46D7-B2D8-8AF36ED85333}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11235" tabRatio="838" xr2:uid="{910269CE-FD31-46D7-B2D8-8AF36ED85333}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -2679,7 +2679,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1035" uniqueCount="723">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1033" uniqueCount="721">
   <si>
     <t>Source:</t>
   </si>
@@ -2748,12 +2748,6 @@
   </si>
   <si>
     <t>Other process</t>
-  </si>
-  <si>
-    <t>green hydrogen if</t>
-  </si>
-  <si>
-    <t>low carbon hydrogen if</t>
   </si>
   <si>
     <t xml:space="preserve">COP: </t>
@@ -7547,6 +7541,12 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="9" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -7568,12 +7568,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="9" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -29431,10 +29425,6 @@
 </externalLink>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -29790,12 +29780,12 @@
         <v>0</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="B4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -29805,227 +29795,227 @@
     </row>
     <row r="6" spans="1:2">
       <c r="B6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="B7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="B8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="B10" s="6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="B11" s="7" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="B12" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="B13" s="7" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="B14" s="48" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="B15" s="7" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
     </row>
     <row r="17" spans="2:2">
       <c r="B17" s="49" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="18" spans="2:2">
       <c r="B18" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="19" spans="2:2">
       <c r="B19" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="20" spans="2:2">
       <c r="B20" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="21" spans="2:2">
       <c r="B21" s="50" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="22" spans="2:2">
       <c r="B22" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
     </row>
     <row r="23" spans="2:2">
       <c r="B23" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
     </row>
     <row r="25" spans="2:2">
       <c r="B25" s="49" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
     </row>
     <row r="26" spans="2:2">
       <c r="B26" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
     </row>
     <row r="27" spans="2:2">
       <c r="B27" s="15" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
     </row>
     <row r="28" spans="2:2">
       <c r="B28" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
     </row>
     <row r="29" spans="2:2">
       <c r="B29" s="51" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
     </row>
     <row r="31" spans="2:2">
       <c r="B31" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="32" spans="2:2">
       <c r="B32" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="33" spans="2:2">
       <c r="B33" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="34" spans="2:2">
       <c r="B34" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="35" spans="2:2">
       <c r="B35" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="37" spans="2:2">
       <c r="B37" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="38" spans="2:2">
       <c r="B38" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="39" spans="2:2">
       <c r="B39" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="40" spans="2:2">
       <c r="B40" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="41" spans="2:2">
       <c r="B41" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="44" spans="2:2">
       <c r="B44" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="46" spans="2:2">
       <c r="B46" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="47" spans="2:2">
       <c r="B47" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="48" spans="2:2">
       <c r="B48" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="B49" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="B50" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="B51" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="B53" s="49" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="B54" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="B55" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="B56" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="B57" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="B58" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="B59" s="15" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
     </row>
     <row r="60" spans="1:2">
@@ -30068,82 +30058,82 @@
     </row>
     <row r="70" spans="1:1">
       <c r="A70" s="1" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" s="15" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" s="15" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
     </row>
     <row r="82" spans="1:1">
       <c r="A82" s="15" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
     </row>
     <row r="83" spans="1:1">
       <c r="A83" s="15" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
     </row>
     <row r="84" spans="1:1">
       <c r="A84" s="15" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" s="196" t="s">
         <v>720</v>
-      </c>
-    </row>
-    <row r="85" spans="1:1">
-      <c r="A85" s="203" t="s">
-        <v>722</v>
       </c>
     </row>
   </sheetData>
@@ -30170,7 +30160,7 @@
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="35" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B1" s="35"/>
       <c r="C1" s="35"/>
@@ -30182,33 +30172,33 @@
     </row>
     <row r="2" spans="1:8" ht="30">
       <c r="A2" s="37" t="s">
+        <v>242</v>
+      </c>
+      <c r="B2" s="37" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" s="37" t="s">
+        <v>243</v>
+      </c>
+      <c r="D2" s="38" t="s">
         <v>244</v>
       </c>
-      <c r="B2" s="37" t="s">
-        <v>53</v>
-      </c>
-      <c r="C2" s="37" t="s">
-        <v>245</v>
-      </c>
-      <c r="D2" s="38" t="s">
-        <v>246</v>
-      </c>
       <c r="E2" s="55" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="F2" s="55" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B3" s="14">
         <v>0.8</v>
       </c>
       <c r="C3" s="58" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D3" s="12">
         <f>(E3/$E$5)*(1-F3)</f>
@@ -30223,13 +30213,13 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="B4" s="14">
         <v>0.88</v>
       </c>
       <c r="C4" s="16" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D4" s="12">
         <f>(E4/$E$5)*(1-F4)</f>
@@ -30244,13 +30234,13 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B5" s="14">
         <v>0.92</v>
       </c>
       <c r="C5" s="58" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="D5" s="12">
         <f>(E5/$E$5)*(1-F5)</f>
@@ -30265,7 +30255,7 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="37" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B7" s="39"/>
       <c r="C7" s="39"/>
@@ -30277,7 +30267,7 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="51" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -30285,52 +30275,52 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="45" customHeight="1">
-      <c r="A40" s="191" t="s">
-        <v>255</v>
-      </c>
-      <c r="B40" s="191"/>
-      <c r="C40" s="191"/>
-      <c r="D40" s="191"/>
+      <c r="A40" s="197" t="s">
+        <v>253</v>
+      </c>
+      <c r="B40" s="197"/>
+      <c r="C40" s="197"/>
+      <c r="D40" s="197"/>
     </row>
     <row r="42" spans="1:5" ht="30">
       <c r="A42" s="40" t="s">
+        <v>254</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="C42" s="10" t="s">
         <v>256</v>
       </c>
-      <c r="B42" s="10" t="s">
+      <c r="D42" s="10" t="s">
         <v>257</v>
       </c>
-      <c r="C42" s="10" t="s">
-        <v>258</v>
-      </c>
-      <c r="D42" s="10" t="s">
-        <v>259</v>
-      </c>
       <c r="E42" s="40" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="B43">
         <v>200</v>
@@ -30342,12 +30332,12 @@
         <v>0.85</v>
       </c>
       <c r="E43" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="B44">
         <v>300</v>
@@ -30361,7 +30351,7 @@
     </row>
     <row r="45" spans="1:5">
       <c r="A45" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B45">
         <v>600</v>
@@ -30375,7 +30365,7 @@
     </row>
     <row r="46" spans="1:5">
       <c r="A46" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="B46">
         <v>1400</v>
@@ -30389,7 +30379,7 @@
     </row>
     <row r="47" spans="1:5">
       <c r="A47" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B47">
         <v>2600</v>
@@ -30403,7 +30393,7 @@
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="37" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B49" s="39"/>
       <c r="C49" s="39"/>
@@ -30411,21 +30401,21 @@
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="40" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B50" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="C50" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="D50" s="10" t="s">
         <v>267</v>
-      </c>
-      <c r="C50" s="10" t="s">
-        <v>268</v>
-      </c>
-      <c r="D50" s="10" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B51" s="14">
         <f>D43*$D$3</f>
@@ -30442,7 +30432,7 @@
     </row>
     <row r="52" spans="1:8">
       <c r="A52" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B52" s="14">
         <f t="shared" ref="B52:B55" si="0">D44*$D$3</f>
@@ -30459,7 +30449,7 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B53" s="14">
         <f t="shared" si="0"/>
@@ -30476,7 +30466,7 @@
     </row>
     <row r="54" spans="1:8">
       <c r="A54" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B54" s="14">
         <f t="shared" si="0"/>
@@ -30493,7 +30483,7 @@
     </row>
     <row r="55" spans="1:8">
       <c r="A55" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B55" s="14">
         <f t="shared" si="0"/>
@@ -30510,7 +30500,7 @@
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="35" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B57" s="36"/>
       <c r="C57" s="36"/>
@@ -30522,7 +30512,7 @@
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="37" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="B58" s="37"/>
       <c r="C58" s="37"/>
@@ -30530,37 +30520,37 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="51" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
     </row>
     <row r="81" spans="1:5">
       <c r="A81" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
     </row>
     <row r="83" spans="1:5">
       <c r="A83" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
     </row>
     <row r="84" spans="1:5">
       <c r="A84" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="85" spans="1:5">
       <c r="A85" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="86" spans="1:5">
       <c r="A86" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="87" spans="1:5">
@@ -30572,21 +30562,21 @@
     </row>
     <row r="88" spans="1:5" ht="90">
       <c r="A88" s="43" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B88" s="44" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="C88" s="44" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="E88" s="158" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
     </row>
     <row r="89" spans="1:5">
       <c r="A89" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B89" s="45">
         <v>90</v>
@@ -30598,7 +30588,7 @@
     </row>
     <row r="90" spans="1:5">
       <c r="A90" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B90" s="45">
         <v>150</v>
@@ -30610,7 +30600,7 @@
     </row>
     <row r="91" spans="1:5">
       <c r="A91" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B91" s="45">
         <v>350</v>
@@ -30622,7 +30612,7 @@
     </row>
     <row r="92" spans="1:5">
       <c r="A92" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B92" s="45">
         <v>750</v>
@@ -30638,7 +30628,7 @@
     </row>
     <row r="93" spans="1:5">
       <c r="A93" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B93" s="45">
         <v>1500</v>
@@ -30661,7 +30651,7 @@
     </row>
     <row r="95" spans="1:5">
       <c r="A95" s="37" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="B95" s="39"/>
       <c r="C95" s="39"/>
@@ -30670,21 +30660,21 @@
     </row>
     <row r="96" spans="1:5">
       <c r="A96" s="40" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B96" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="C96" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="D96" s="10" t="s">
         <v>267</v>
-      </c>
-      <c r="C96" s="10" t="s">
-        <v>268</v>
-      </c>
-      <c r="D96" s="10" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B97" s="14">
         <f>C89*$D$3</f>
@@ -30701,7 +30691,7 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B98" s="14">
         <f>C90*$D$3</f>
@@ -30718,7 +30708,7 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B99" s="14">
         <f>C91*$D$3</f>
@@ -30735,7 +30725,7 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B100" s="14">
         <f>C92*$D$3</f>
@@ -30752,7 +30742,7 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B101" s="14">
         <f>C93*$D$3</f>
@@ -30769,7 +30759,7 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" s="55" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="B103" s="56"/>
       <c r="C103" s="56"/>
@@ -30778,27 +30768,27 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" s="1" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B104" s="57" t="s">
+        <v>265</v>
+      </c>
+      <c r="C104" s="57" t="s">
+        <v>266</v>
+      </c>
+      <c r="D104" s="57" t="s">
         <v>267</v>
       </c>
-      <c r="C104" s="57" t="s">
-        <v>268</v>
-      </c>
-      <c r="D104" s="57" t="s">
-        <v>269</v>
-      </c>
       <c r="E104" s="57" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F104" s="57" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
     </row>
     <row r="105" spans="1:6">
       <c r="A105" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B105" s="11">
         <f>$F105*B$139+(1-$F105)*($E105*B97+(1-$E105)*B51)*$C$144</f>
@@ -30821,7 +30811,7 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B106" s="11">
         <f>$F106*B$139+(1-$F106)*($E106*B98+(1-$E106)*B52)*$C$145</f>
@@ -30844,7 +30834,7 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="B107" s="11">
         <f>$F107*B$139+(1-$F107)*($E107*B99+(1-$E107)*B53)*$C$146</f>
@@ -30867,7 +30857,7 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="B108" s="11">
         <f>$F108*B$139+(1-$F108)*($E108*B100+(1-$E108)*B54)*$C$147</f>
@@ -30891,7 +30881,7 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B109" s="23">
         <f>$B$163*($F109*B$139+(1-$F109)*($E109*B101+(1-$E109)*B55)*$C$148)+(1-$B$163)*$B$164</f>
@@ -30915,87 +30905,87 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" s="55" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B111" s="55"/>
     </row>
     <row r="112" spans="1:6">
       <c r="A112" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
     </row>
     <row r="113" spans="1:4">
       <c r="A113" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="114" spans="1:4">
       <c r="A114" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
     </row>
     <row r="115" spans="1:4">
       <c r="A115" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
     </row>
     <row r="116" spans="1:4">
       <c r="A116" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
     </row>
     <row r="117" spans="1:4">
       <c r="A117" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
     </row>
     <row r="118" spans="1:4">
       <c r="A118" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
     </row>
     <row r="119" spans="1:4">
       <c r="A119" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
     </row>
     <row r="120" spans="1:4">
       <c r="A120" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
     </row>
     <row r="121" spans="1:4">
       <c r="A121" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
     </row>
     <row r="122" spans="1:4">
       <c r="A122" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="55" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="125" spans="1:4" ht="30">
       <c r="A125" t="s">
+        <v>459</v>
+      </c>
+      <c r="B125" s="57" t="s">
+        <v>460</v>
+      </c>
+      <c r="C125" s="10" t="s">
         <v>461</v>
       </c>
-      <c r="B125" s="57" t="s">
+      <c r="D125" s="10" t="s">
         <v>462</v>
-      </c>
-      <c r="C125" s="10" t="s">
-        <v>463</v>
-      </c>
-      <c r="D125" s="10" t="s">
-        <v>464</v>
       </c>
     </row>
     <row r="126" spans="1:4">
       <c r="A126" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B126" s="11">
         <f>'Kermeli Data'!C12</f>
@@ -31012,7 +31002,7 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B127" s="11">
         <f>'Kermeli Data'!C15</f>
@@ -31029,7 +31019,7 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="B128" s="34">
         <v>0.8</v>
@@ -31045,7 +31035,7 @@
     </row>
     <row r="129" spans="1:5">
       <c r="A129" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B129" s="34">
         <v>0.9</v>
@@ -31061,7 +31051,7 @@
     </row>
     <row r="130" spans="1:5">
       <c r="A130" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B130" s="157">
         <f>'Kermeli Data'!C106</f>
@@ -31078,7 +31068,7 @@
     </row>
     <row r="131" spans="1:5">
       <c r="A131" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B131" s="34">
         <v>0.1</v>
@@ -31094,7 +31084,7 @@
     </row>
     <row r="133" spans="1:5">
       <c r="A133" s="1" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B133" s="11">
         <f>IF(OR(SUM(C126:C131)=0,COUNTBLANK($B$126:$B$131)&gt;0),"pending diffusion inputs",SUMPRODUCT(B126:B131,C126:C131)/SUM(C126:C131))</f>
@@ -31103,7 +31093,7 @@
     </row>
     <row r="134" spans="1:5">
       <c r="A134" s="1" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="B134" s="11">
         <f>IF(OR(SUM(D126:D131)=0,COUNTBLANK($B$126:$B$131)&gt;0),"pending diffusion inputs",SUMPRODUCT(B126:B131,D126:D131)/SUM(D126:D131))</f>
@@ -31112,7 +31102,7 @@
     </row>
     <row r="136" spans="1:5">
       <c r="A136" s="55" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B136" s="56"/>
       <c r="C136" s="56"/>
@@ -31121,7 +31111,7 @@
     </row>
     <row r="137" spans="1:5">
       <c r="A137" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="B137" s="34">
         <v>0.12</v>
@@ -31129,7 +31119,7 @@
     </row>
     <row r="139" spans="1:5">
       <c r="A139" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="B139" s="11">
         <f>B$140*(1-$B$137)</f>
@@ -31146,7 +31136,7 @@
     </row>
     <row r="140" spans="1:5">
       <c r="A140" s="2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B140" s="161">
         <v>0.90300000000000002</v>
@@ -31160,7 +31150,7 @@
     </row>
     <row r="142" spans="1:5">
       <c r="A142" s="55" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B142" s="56"/>
       <c r="C142" s="56"/>
@@ -31168,18 +31158,18 @@
     </row>
     <row r="143" spans="1:5">
       <c r="A143" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="C143" s="1" t="s">
         <v>670</v>
-      </c>
-      <c r="B143" s="1" t="s">
-        <v>671</v>
-      </c>
-      <c r="C143" s="1" t="s">
-        <v>672</v>
       </c>
     </row>
     <row r="144" spans="1:5">
       <c r="A144" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="B144" s="23" cm="1">
         <f t="array" ref="B144">SUMPRODUCT('indst heat consumption'!I$4:I$28,1-'indst heat consumption'!$N$4:$N$28)</f>
@@ -31191,7 +31181,7 @@
     </row>
     <row r="145" spans="1:4">
       <c r="A145" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B145" s="23" cm="1">
         <f t="array" ref="B145">SUMPRODUCT('indst heat consumption'!J$4:J$28,1-'indst heat consumption'!$N$4:$N$28)</f>
@@ -31203,7 +31193,7 @@
     </row>
     <row r="146" spans="1:4">
       <c r="A146" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="B146" s="23" cm="1">
         <f t="array" ref="B146">SUMPRODUCT('indst heat consumption'!K$4:K$28,1-'indst heat consumption'!$N$4:$N$28)</f>
@@ -31216,7 +31206,7 @@
     </row>
     <row r="147" spans="1:4">
       <c r="A147" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B147" s="23" cm="1">
         <f t="array" ref="B147">SUMPRODUCT('indst heat consumption'!L$4:L$28,1-'indst heat consumption'!$N$4:$N$28)</f>
@@ -31229,7 +31219,7 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="B148" s="23" cm="1">
         <f t="array" ref="B148">SUMPRODUCT('indst heat consumption'!M$4:M$28,1-'indst heat consumption'!$N$4:$N$28)</f>
@@ -31241,17 +31231,17 @@
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="163" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="55" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
     </row>
     <row r="152" spans="1:4">
       <c r="A152" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B152" s="164">
         <f>'indst heat consumption'!K6+'indst heat consumption'!K12+'indst heat consumption'!K13+'indst heat consumption'!K14</f>
@@ -31260,7 +31250,7 @@
     </row>
     <row r="153" spans="1:4">
       <c r="A153" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="B153" s="164">
         <f>'indst heat consumption'!L6+'indst heat consumption'!L12+'indst heat consumption'!L13+'indst heat consumption'!L14</f>
@@ -31269,7 +31259,7 @@
     </row>
     <row r="154" spans="1:4">
       <c r="A154" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="B154" s="164">
         <f>'Electric Process Heat'!B7/'Heat pumps'!H25</f>
@@ -31278,31 +31268,31 @@
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="2" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
     </row>
     <row r="157" spans="1:4">
-      <c r="A157" s="198" t="s">
+      <c r="A157" s="191" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4">
+      <c r="A158" s="192" t="s">
+        <v>700</v>
+      </c>
+      <c r="B158" s="192" t="s">
+        <v>462</v>
+      </c>
+      <c r="C158" s="192" t="s">
         <v>701</v>
       </c>
-    </row>
-    <row r="158" spans="1:4">
-      <c r="A158" s="199" t="s">
+      <c r="D158" s="192" t="s">
         <v>702</v>
-      </c>
-      <c r="B158" s="199" t="s">
-        <v>464</v>
-      </c>
-      <c r="C158" s="199" t="s">
-        <v>703</v>
-      </c>
-      <c r="D158" s="199" t="s">
-        <v>704</v>
       </c>
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="15" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="B159" s="164">
         <f>'indst heat consumption'!M15</f>
@@ -31312,12 +31302,12 @@
         <v>1</v>
       </c>
       <c r="D159" s="15" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="15" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="B160" s="164">
         <f>'indst heat consumption'!M19+'indst heat consumption'!M18</f>
@@ -31327,12 +31317,12 @@
         <v>1</v>
       </c>
       <c r="D160" s="15" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
     </row>
     <row r="161" spans="1:4">
       <c r="A161" s="15" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="B161" s="164">
         <f>'indst heat consumption'!M17</f>
@@ -31342,12 +31332,12 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="D161" s="15" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="15" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B162" s="164">
         <f>'indst heat consumption'!M16</f>
@@ -31357,23 +31347,23 @@
         <v>0</v>
       </c>
       <c r="D162" s="15" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
     </row>
     <row r="163" spans="1:4">
-      <c r="A163" s="199" t="s">
-        <v>712</v>
-      </c>
-      <c r="B163" s="200">
+      <c r="A163" s="192" t="s">
+        <v>710</v>
+      </c>
+      <c r="B163" s="193">
         <f>SUMPRODUCT(B159:B162,C159:C162)/SUM(B159:B162)</f>
         <v>0.54221639527744547</v>
       </c>
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="15" t="s">
-        <v>713</v>
-      </c>
-      <c r="B164" s="201">
+        <v>711</v>
+      </c>
+      <c r="B164" s="194">
         <v>0.5</v>
       </c>
     </row>
@@ -31410,22 +31400,22 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1">
       <c r="A1" s="30" t="s">
+        <v>185</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="C1" s="31" t="s">
         <v>187</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="E1" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>190</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -31433,16 +31423,16 @@
         <v>19</v>
       </c>
       <c r="B2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C2" s="25">
         <v>2014</v>
       </c>
       <c r="D2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="E2" s="16" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -31450,16 +31440,16 @@
         <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C3" s="25">
         <v>2016</v>
       </c>
       <c r="D3" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -31467,16 +31457,16 @@
         <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C4" s="25">
         <v>2020</v>
       </c>
       <c r="D4" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -31484,16 +31474,16 @@
         <v>22</v>
       </c>
       <c r="B5" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C5" s="25">
         <v>2022</v>
       </c>
       <c r="D5" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -31501,16 +31491,16 @@
         <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C6" s="25">
         <v>2021</v>
       </c>
       <c r="D6" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -31518,16 +31508,16 @@
         <v>24</v>
       </c>
       <c r="B7" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="C7" s="25">
         <v>2018</v>
       </c>
       <c r="D7" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -31535,16 +31525,16 @@
         <v>25</v>
       </c>
       <c r="B8" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C8" s="25">
         <v>2015</v>
       </c>
       <c r="D8" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E8" s="16" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -31552,19 +31542,19 @@
         <v>26</v>
       </c>
       <c r="B9" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C9" s="25">
         <v>2016</v>
       </c>
       <c r="D9" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="E9" s="50" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="F9" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -31572,19 +31562,19 @@
         <v>27</v>
       </c>
       <c r="B10" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C10" s="25">
         <v>2020</v>
       </c>
       <c r="D10" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="E10" s="50" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="F10" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -31592,19 +31582,19 @@
         <v>28</v>
       </c>
       <c r="B11" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="C11" s="25">
         <v>2022</v>
       </c>
       <c r="D11" t="s">
+        <v>513</v>
+      </c>
+      <c r="E11" s="50" t="s">
+        <v>514</v>
+      </c>
+      <c r="F11" t="s">
         <v>515</v>
-      </c>
-      <c r="E11" s="50" t="s">
-        <v>516</v>
-      </c>
-      <c r="F11" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -31612,19 +31602,19 @@
         <v>29</v>
       </c>
       <c r="B12" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="C12" s="25">
         <v>2020</v>
       </c>
       <c r="D12" t="s">
+        <v>536</v>
+      </c>
+      <c r="E12" s="50" t="s">
+        <v>537</v>
+      </c>
+      <c r="F12" t="s">
         <v>538</v>
-      </c>
-      <c r="E12" s="50" t="s">
-        <v>539</v>
-      </c>
-      <c r="F12" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -31632,19 +31622,19 @@
         <v>30</v>
       </c>
       <c r="B13" t="s">
+        <v>539</v>
+      </c>
+      <c r="C13" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="D13" t="s">
+        <v>540</v>
+      </c>
+      <c r="E13" s="50" t="s">
         <v>541</v>
       </c>
-      <c r="C13" s="25" t="s">
-        <v>90</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="F13" t="s">
         <v>542</v>
-      </c>
-      <c r="E13" s="50" t="s">
-        <v>543</v>
-      </c>
-      <c r="F13" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -31652,19 +31642,19 @@
         <v>31</v>
       </c>
       <c r="B14" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="C14" s="25">
         <v>2003</v>
       </c>
       <c r="D14" t="s">
+        <v>544</v>
+      </c>
+      <c r="E14" s="50" t="s">
+        <v>545</v>
+      </c>
+      <c r="F14" t="s">
         <v>546</v>
-      </c>
-      <c r="E14" s="50" t="s">
-        <v>547</v>
-      </c>
-      <c r="F14" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -31672,19 +31662,19 @@
         <v>32</v>
       </c>
       <c r="B15" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="C15" s="25" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D15" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E15" s="50" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F15" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -31692,19 +31682,19 @@
         <v>33</v>
       </c>
       <c r="B16" t="s">
+        <v>549</v>
+      </c>
+      <c r="C16" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="D16" t="s">
+        <v>550</v>
+      </c>
+      <c r="E16" s="50" t="s">
         <v>551</v>
       </c>
-      <c r="C16" s="25" t="s">
-        <v>90</v>
-      </c>
-      <c r="D16" t="s">
+      <c r="F16" t="s">
         <v>552</v>
-      </c>
-      <c r="E16" s="50" t="s">
-        <v>553</v>
-      </c>
-      <c r="F16" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -31712,19 +31702,19 @@
         <v>34</v>
       </c>
       <c r="B17" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="C17" s="25">
         <v>2026</v>
       </c>
       <c r="D17" t="s">
+        <v>557</v>
+      </c>
+      <c r="E17" s="50" t="s">
+        <v>558</v>
+      </c>
+      <c r="F17" t="s">
         <v>559</v>
-      </c>
-      <c r="E17" s="50" t="s">
-        <v>560</v>
-      </c>
-      <c r="F17" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -31732,19 +31722,19 @@
         <v>35</v>
       </c>
       <c r="B18" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="C18" s="25">
         <v>2004</v>
       </c>
       <c r="D18" t="s">
+        <v>625</v>
+      </c>
+      <c r="E18" s="50" t="s">
+        <v>626</v>
+      </c>
+      <c r="F18" t="s">
         <v>627</v>
-      </c>
-      <c r="E18" s="50" t="s">
-        <v>628</v>
-      </c>
-      <c r="F18" t="s">
-        <v>629</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -31752,19 +31742,19 @@
         <v>36</v>
       </c>
       <c r="B19" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C19" s="25">
         <v>2015</v>
       </c>
       <c r="D19" t="s">
+        <v>628</v>
+      </c>
+      <c r="E19" s="50" t="s">
+        <v>629</v>
+      </c>
+      <c r="F19" t="s">
         <v>630</v>
-      </c>
-      <c r="E19" s="50" t="s">
-        <v>631</v>
-      </c>
-      <c r="F19" t="s">
-        <v>632</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -31772,19 +31762,19 @@
         <v>37</v>
       </c>
       <c r="B20" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C20" s="25">
         <v>2019</v>
       </c>
       <c r="D20" t="s">
+        <v>632</v>
+      </c>
+      <c r="E20" s="50" t="s">
+        <v>633</v>
+      </c>
+      <c r="F20" t="s">
         <v>634</v>
-      </c>
-      <c r="E20" s="50" t="s">
-        <v>635</v>
-      </c>
-      <c r="F20" t="s">
-        <v>636</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -31792,19 +31782,19 @@
         <v>38</v>
       </c>
       <c r="B21" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="C21" s="25">
         <v>2009</v>
       </c>
       <c r="D21" t="s">
+        <v>636</v>
+      </c>
+      <c r="E21" s="50" t="s">
+        <v>637</v>
+      </c>
+      <c r="F21" t="s">
         <v>638</v>
-      </c>
-      <c r="E21" s="50" t="s">
-        <v>639</v>
-      </c>
-      <c r="F21" t="s">
-        <v>640</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -31812,19 +31802,19 @@
         <v>39</v>
       </c>
       <c r="B22" t="s">
+        <v>639</v>
+      </c>
+      <c r="C22" s="25" t="s">
+        <v>88</v>
+      </c>
+      <c r="D22" t="s">
+        <v>640</v>
+      </c>
+      <c r="E22" s="50" t="s">
         <v>641</v>
       </c>
-      <c r="C22" s="25" t="s">
-        <v>90</v>
-      </c>
-      <c r="D22" t="s">
+      <c r="F22" t="s">
         <v>642</v>
-      </c>
-      <c r="E22" s="50" t="s">
-        <v>643</v>
-      </c>
-      <c r="F22" t="s">
-        <v>644</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -31832,19 +31822,19 @@
         <v>40</v>
       </c>
       <c r="B23" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="C23" s="25">
         <v>2012</v>
       </c>
       <c r="D23" t="s">
+        <v>646</v>
+      </c>
+      <c r="E23" s="50" t="s">
+        <v>647</v>
+      </c>
+      <c r="F23" t="s">
         <v>648</v>
-      </c>
-      <c r="E23" s="50" t="s">
-        <v>649</v>
-      </c>
-      <c r="F23" t="s">
-        <v>650</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -31852,19 +31842,19 @@
         <v>41</v>
       </c>
       <c r="B24" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="C24" s="25">
         <v>2016</v>
       </c>
       <c r="D24" t="s">
+        <v>650</v>
+      </c>
+      <c r="E24" s="50" t="s">
+        <v>651</v>
+      </c>
+      <c r="F24" t="s">
         <v>652</v>
-      </c>
-      <c r="E24" s="50" t="s">
-        <v>653</v>
-      </c>
-      <c r="F24" t="s">
-        <v>654</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -31872,19 +31862,19 @@
         <v>42</v>
       </c>
       <c r="B25" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C25" s="190">
         <v>2011</v>
       </c>
       <c r="D25" t="s">
+        <v>680</v>
+      </c>
+      <c r="E25" s="50" t="s">
+        <v>681</v>
+      </c>
+      <c r="F25" t="s">
         <v>682</v>
-      </c>
-      <c r="E25" s="50" t="s">
-        <v>683</v>
-      </c>
-      <c r="F25" t="s">
-        <v>684</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -31892,19 +31882,19 @@
         <v>43</v>
       </c>
       <c r="B26" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="C26" s="190">
         <v>2018</v>
       </c>
       <c r="D26" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E26" s="50" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F26" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -31912,19 +31902,19 @@
         <v>44</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="C27" s="25">
         <v>2023</v>
       </c>
       <c r="D27" s="15" t="s">
+        <v>713</v>
+      </c>
+      <c r="E27" s="195" t="s">
+        <v>714</v>
+      </c>
+      <c r="F27" s="15" t="s">
         <v>715</v>
-      </c>
-      <c r="E27" s="202" t="s">
-        <v>716</v>
-      </c>
-      <c r="F27" s="15" t="s">
-        <v>717</v>
       </c>
     </row>
   </sheetData>
@@ -31952,7 +31942,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="18.75">
       <c r="A1" s="165" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="B1" s="166"/>
       <c r="C1" s="166"/>
@@ -31963,7 +31953,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="167" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B2" s="166"/>
       <c r="C2" s="166"/>
@@ -31983,7 +31973,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="168" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="B4" s="169"/>
       <c r="C4" s="169"/>
@@ -31994,28 +31984,28 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="170" t="s">
+        <v>563</v>
+      </c>
+      <c r="B5" s="171" t="s">
+        <v>564</v>
+      </c>
+      <c r="C5" s="171" t="s">
+        <v>566</v>
+      </c>
+      <c r="D5" s="171" t="s">
+        <v>567</v>
+      </c>
+      <c r="E5" s="170" t="s">
         <v>565</v>
       </c>
-      <c r="B5" s="171" t="s">
-        <v>566</v>
-      </c>
-      <c r="C5" s="171" t="s">
-        <v>568</v>
-      </c>
-      <c r="D5" s="171" t="s">
-        <v>569</v>
-      </c>
-      <c r="E5" s="170" t="s">
-        <v>567</v>
-      </c>
       <c r="F5" s="171" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="G5" s="166"/>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="166" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="B6" s="172">
         <v>0.97</v>
@@ -32027,16 +32017,16 @@
         <v>0.99</v>
       </c>
       <c r="E6" s="166" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="F6" s="166" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="G6" s="166"/>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="166" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="B7" s="172">
         <v>0.8</v>
@@ -32048,16 +32038,16 @@
         <v>0.88</v>
       </c>
       <c r="E7" s="166" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="F7" s="166" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="G7" s="166"/>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="166" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="B8" s="173">
         <v>0.67500000000000004</v>
@@ -32069,16 +32059,16 @@
         <v>0.76</v>
       </c>
       <c r="E8" s="166" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="F8" s="166" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="G8" s="166"/>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="166" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="B9" s="173">
         <v>0.65</v>
@@ -32090,16 +32080,16 @@
         <v>0.7</v>
       </c>
       <c r="E9" s="166" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="F9" s="166" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="G9" s="166"/>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="166" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="B10" s="173">
         <v>0.6</v>
@@ -32111,10 +32101,10 @@
         <v>0.9</v>
       </c>
       <c r="E10" s="166" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="F10" s="166" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="G10" s="166"/>
     </row>
@@ -32129,7 +32119,7 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="168" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B12" s="169"/>
       <c r="C12" s="169"/>
@@ -32140,7 +32130,7 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="167" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B13" s="166"/>
       <c r="C13" s="166"/>
@@ -32151,30 +32141,30 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="170" t="s">
+        <v>585</v>
+      </c>
+      <c r="B14" s="171" t="s">
+        <v>586</v>
+      </c>
+      <c r="C14" s="171" t="s">
         <v>587</v>
       </c>
-      <c r="B14" s="171" t="s">
+      <c r="D14" s="171" t="s">
         <v>588</v>
       </c>
-      <c r="C14" s="171" t="s">
+      <c r="E14" s="171" t="s">
         <v>589</v>
       </c>
-      <c r="D14" s="171" t="s">
+      <c r="F14" s="171" t="s">
         <v>590</v>
       </c>
-      <c r="E14" s="171" t="s">
+      <c r="G14" s="171" t="s">
         <v>591</v>
-      </c>
-      <c r="F14" s="171" t="s">
-        <v>592</v>
-      </c>
-      <c r="G14" s="171" t="s">
-        <v>593</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="166" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="B15" s="187">
         <f>'Combustion Efficiency'!F107</f>
@@ -32200,7 +32190,7 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="166" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B16" s="174">
         <v>0</v>
@@ -32233,7 +32223,7 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="168" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="B18" s="169"/>
       <c r="C18" s="169"/>
@@ -32244,30 +32234,30 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="170" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B19" s="171" t="s">
+        <v>593</v>
+      </c>
+      <c r="C19" s="171" t="s">
+        <v>594</v>
+      </c>
+      <c r="D19" s="171" t="s">
         <v>595</v>
       </c>
-      <c r="C19" s="171" t="s">
+      <c r="E19" s="171" t="s">
         <v>596</v>
       </c>
-      <c r="D19" s="171" t="s">
+      <c r="F19" s="171" t="s">
         <v>597</v>
       </c>
-      <c r="E19" s="171" t="s">
+      <c r="G19" s="171" t="s">
         <v>598</v>
-      </c>
-      <c r="F19" s="171" t="s">
-        <v>599</v>
-      </c>
-      <c r="G19" s="171" t="s">
-        <v>600</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="166" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="B20" s="176">
         <f>B15*$B$6*(1-'Combustion Efficiency'!$B$137)+C15*$B$7+D15*$B$8+E15*$B$9+F15*$B$10</f>
@@ -32296,7 +32286,7 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="166" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B21" s="176">
         <f>B16*$B$6*(1-'Combustion Efficiency'!$B$137)+C16*$B$7+D16*$B$8+E16*$B$9+F16*$B$10</f>
@@ -32334,7 +32324,7 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" s="168" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="B23" s="169"/>
       <c r="C23" s="169"/>
@@ -32345,7 +32335,7 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="167" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="B24" s="166"/>
       <c r="C24" s="166"/>
@@ -32356,26 +32346,26 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" s="170" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="B25" s="171" t="s">
+        <v>601</v>
+      </c>
+      <c r="C25" s="171" t="s">
+        <v>602</v>
+      </c>
+      <c r="D25" s="171" t="s">
         <v>603</v>
       </c>
-      <c r="C25" s="171" t="s">
+      <c r="E25" s="171" t="s">
         <v>604</v>
-      </c>
-      <c r="D25" s="171" t="s">
-        <v>605</v>
-      </c>
-      <c r="E25" s="171" t="s">
-        <v>606</v>
       </c>
       <c r="F25" s="166"/>
       <c r="G25" s="166"/>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" s="166" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="B26" s="176">
         <f>B15*$C$6*(1-'Combustion Efficiency'!$B$137)+C15*$C$7+D15*$C$8+E15*$C$9+F15*$C$10</f>
@@ -32398,7 +32388,7 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="166" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="B27" s="176">
         <f>B16*$C$6*(1-'Combustion Efficiency'!$B$137)+C16*$C$7+D16*$C$8+E16*$C$9+F16*$C$10</f>
@@ -32430,7 +32420,7 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" s="180" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="B29" s="166"/>
       <c r="C29" s="166"/>
@@ -32441,7 +32431,7 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" s="181" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="B30" s="166"/>
       <c r="C30" s="166"/>
@@ -32452,7 +32442,7 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="182" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B31" s="166"/>
       <c r="C31" s="166"/>
@@ -32472,7 +32462,7 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" s="183" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="B33" s="166"/>
       <c r="C33" s="166"/>
@@ -32483,7 +32473,7 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" s="181" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="B34" s="166"/>
       <c r="C34" s="166"/>
@@ -32501,7 +32491,7 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" s="183" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="B36" s="166"/>
       <c r="C36" s="166"/>
@@ -32512,7 +32502,7 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" s="184" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="B37" s="166"/>
       <c r="C37" s="166"/>
@@ -32532,7 +32522,7 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" s="168" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="B39" s="169"/>
       <c r="C39" s="169"/>
@@ -32543,7 +32533,7 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" s="181" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="B40" s="166"/>
       <c r="C40" s="166"/>
@@ -32554,14 +32544,14 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" s="166" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="B41" s="185">
         <f>'Heat pumps'!H25</f>
         <v>0.99</v>
       </c>
       <c r="C41" s="166" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="D41" s="166"/>
       <c r="E41" s="166"/>
@@ -32570,7 +32560,7 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" s="166" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="B42" s="176">
         <f>B41/B20-1</f>
@@ -32584,7 +32574,7 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" s="166" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="B43" s="176">
         <f>B41/B21-1</f>
@@ -32598,12 +32588,12 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" s="160" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="55" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B47" s="56"/>
       <c r="C47" s="56"/>
@@ -32611,7 +32601,7 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="B48" s="34">
         <v>0.56999999999999995</v>
@@ -32625,7 +32615,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="B49" s="12">
         <f>1/B48</f>
@@ -32634,7 +32624,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="2" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
     </row>
   </sheetData>
@@ -32654,22 +32644,22 @@
   <sheetData>
     <row r="1" spans="1:8" ht="30">
       <c r="A1" s="54" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B1" s="54" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C1" s="54" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D1" s="54" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E1" s="54" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F1" s="54" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="H1" s="53" t="s">
         <v>0</v>
@@ -32695,7 +32685,7 @@
         <v>0.99950000000000006</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -32741,7 +32731,7 @@
         <v>0.99780000000000002</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -32764,7 +32754,7 @@
         <v>0.997</v>
       </c>
       <c r="H5" s="52" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -35729,7 +35719,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="22" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B1" s="22"/>
       <c r="C1" s="22"/>
@@ -35744,84 +35734,84 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B2" s="59" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="18">
       <c r="A3" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="15.75" thickBot="1"/>
     <row r="7" spans="1:11" ht="15.75" thickBot="1">
-      <c r="A7" s="192" t="s">
-        <v>304</v>
-      </c>
-      <c r="B7" s="193"/>
-      <c r="C7" s="193"/>
-      <c r="D7" s="193"/>
-      <c r="E7" s="193"/>
-      <c r="F7" s="193"/>
-      <c r="G7" s="193"/>
-      <c r="H7" s="193"/>
-      <c r="I7" s="193"/>
-      <c r="J7" s="193"/>
-      <c r="K7" s="194"/>
+      <c r="A7" s="198" t="s">
+        <v>302</v>
+      </c>
+      <c r="B7" s="199"/>
+      <c r="C7" s="199"/>
+      <c r="D7" s="199"/>
+      <c r="E7" s="199"/>
+      <c r="F7" s="199"/>
+      <c r="G7" s="199"/>
+      <c r="H7" s="199"/>
+      <c r="I7" s="199"/>
+      <c r="J7" s="199"/>
+      <c r="K7" s="200"/>
     </row>
     <row r="8" spans="1:11" ht="36.75" thickBot="1">
       <c r="A8" t="s">
+        <v>303</v>
+      </c>
+      <c r="B8" s="60" t="s">
+        <v>304</v>
+      </c>
+      <c r="C8" s="60" t="s">
         <v>305</v>
       </c>
-      <c r="B8" s="60" t="s">
+      <c r="D8" s="60" t="s">
         <v>306</v>
       </c>
-      <c r="C8" s="60" t="s">
+      <c r="E8" s="60" t="s">
         <v>307</v>
       </c>
-      <c r="D8" s="60" t="s">
+      <c r="F8" s="60" t="s">
         <v>308</v>
       </c>
-      <c r="E8" s="60" t="s">
+      <c r="G8" s="60" t="s">
         <v>309</v>
       </c>
-      <c r="F8" s="60" t="s">
+      <c r="H8" s="60" t="s">
         <v>310</v>
       </c>
-      <c r="G8" s="60" t="s">
+      <c r="I8" s="61" t="s">
         <v>311</v>
       </c>
-      <c r="H8" s="60" t="s">
+      <c r="J8" s="61" t="s">
         <v>312</v>
       </c>
-      <c r="I8" s="61" t="s">
+      <c r="K8" s="61" t="s">
         <v>313</v>
-      </c>
-      <c r="J8" s="61" t="s">
-        <v>314</v>
-      </c>
-      <c r="K8" s="61" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="15.75" thickBot="1">
       <c r="A9" s="62" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B9" s="62" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C9" s="63">
         <v>0.9</v>
@@ -35853,10 +35843,10 @@
     </row>
     <row r="10" spans="1:11" ht="15.75" thickBot="1">
       <c r="A10" s="66" t="s">
+        <v>314</v>
+      </c>
+      <c r="B10" s="66" t="s">
         <v>316</v>
-      </c>
-      <c r="B10" s="66" t="s">
-        <v>318</v>
       </c>
       <c r="C10" s="67">
         <v>0.55000000000000004</v>
@@ -35888,10 +35878,10 @@
     </row>
     <row r="11" spans="1:11" ht="15.75" thickBot="1">
       <c r="A11" s="69" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B11" s="69" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C11" s="70">
         <v>0.55000000000000004</v>
@@ -35923,10 +35913,10 @@
     </row>
     <row r="12" spans="1:11" ht="15.75" thickBot="1">
       <c r="A12" s="72" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B12" s="72" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C12" s="73">
         <v>0.3</v>
@@ -35958,10 +35948,10 @@
     </row>
     <row r="13" spans="1:11" ht="15.75" thickBot="1">
       <c r="A13" s="69" t="s">
+        <v>318</v>
+      </c>
+      <c r="B13" s="69" t="s">
         <v>320</v>
-      </c>
-      <c r="B13" s="69" t="s">
-        <v>322</v>
       </c>
       <c r="C13" s="70">
         <v>0</v>
@@ -35993,10 +35983,10 @@
     </row>
     <row r="14" spans="1:11" ht="15.75" thickBot="1">
       <c r="A14" s="76" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B14" s="76" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C14" s="74">
         <v>0.6</v>
@@ -36028,10 +36018,10 @@
     </row>
     <row r="15" spans="1:11" ht="15.75" thickBot="1">
       <c r="A15" s="77" t="s">
+        <v>321</v>
+      </c>
+      <c r="B15" s="77" t="s">
         <v>323</v>
-      </c>
-      <c r="B15" s="77" t="s">
-        <v>325</v>
       </c>
       <c r="C15" s="78">
         <v>0.5</v>
@@ -36063,10 +36053,10 @@
     </row>
     <row r="16" spans="1:11" ht="15.75" thickBot="1">
       <c r="A16" s="81" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B16" s="81" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C16" s="82">
         <v>0.05</v>
@@ -36098,10 +36088,10 @@
     </row>
     <row r="17" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A17" s="76" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B17" s="76" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C17" s="74">
         <v>0.3</v>
@@ -36133,10 +36123,10 @@
     </row>
     <row r="18" spans="1:11" ht="15.75" thickBot="1">
       <c r="A18" s="66" t="s">
+        <v>325</v>
+      </c>
+      <c r="B18" s="66" t="s">
         <v>327</v>
-      </c>
-      <c r="B18" s="66" t="s">
-        <v>329</v>
       </c>
       <c r="C18" s="67">
         <v>0.3</v>
@@ -36168,10 +36158,10 @@
     </row>
     <row r="19" spans="1:11" ht="15.75" thickBot="1">
       <c r="A19" s="69" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B19" s="69" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C19" s="70">
         <v>0.3</v>
@@ -36203,10 +36193,10 @@
     </row>
     <row r="20" spans="1:11" ht="15.75" thickBot="1">
       <c r="A20" s="76" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B20" s="76" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C20" s="74">
         <v>0</v>
@@ -36238,10 +36228,10 @@
     </row>
     <row r="21" spans="1:11" ht="15.75" thickBot="1">
       <c r="A21" s="66" t="s">
+        <v>329</v>
+      </c>
+      <c r="B21" s="66" t="s">
         <v>331</v>
-      </c>
-      <c r="B21" s="66" t="s">
-        <v>333</v>
       </c>
       <c r="C21" s="67">
         <v>0.7</v>
@@ -36273,10 +36263,10 @@
     </row>
     <row r="22" spans="1:11" ht="15.75" thickBot="1">
       <c r="A22" s="85" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B22" s="85" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C22" s="79">
         <v>0.05</v>
@@ -36308,10 +36298,10 @@
     </row>
     <row r="23" spans="1:11" ht="15.75" thickBot="1">
       <c r="A23" s="66" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B23" s="66" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C23" s="67">
         <v>0.05</v>
@@ -36343,10 +36333,10 @@
     </row>
     <row r="24" spans="1:11" ht="15.75" thickBot="1">
       <c r="A24" s="85" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B24" s="85" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C24" s="79">
         <v>0.05</v>
@@ -36378,10 +36368,10 @@
     </row>
     <row r="25" spans="1:11" ht="15.75" thickBot="1">
       <c r="A25" s="66" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B25" s="66" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C25" s="67">
         <v>0.05</v>
@@ -36413,10 +36403,10 @@
     </row>
     <row r="26" spans="1:11" ht="15.75" thickBot="1">
       <c r="A26" s="85" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B26" s="85" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C26" s="79">
         <v>0.25</v>
@@ -36448,10 +36438,10 @@
     </row>
     <row r="27" spans="1:11" ht="15.75" thickBot="1">
       <c r="A27" s="86" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B27" s="86" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C27" s="87">
         <v>0.5</v>
@@ -36483,10 +36473,10 @@
     </row>
     <row r="28" spans="1:11" ht="15.75" thickBot="1">
       <c r="A28" s="66" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B28" s="66" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C28" s="67">
         <v>0.7</v>
@@ -36518,10 +36508,10 @@
     </row>
     <row r="29" spans="1:11" ht="15.75" thickBot="1">
       <c r="A29" s="85" t="s">
+        <v>338</v>
+      </c>
+      <c r="B29" s="85" t="s">
         <v>340</v>
-      </c>
-      <c r="B29" s="85" t="s">
-        <v>342</v>
       </c>
       <c r="C29" s="78">
         <v>0.3</v>
@@ -36553,10 +36543,10 @@
     </row>
     <row r="30" spans="1:11" ht="15.75" thickBot="1">
       <c r="A30" s="66" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B30" s="66" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C30" s="67">
         <v>0.85</v>
@@ -36588,10 +36578,10 @@
     </row>
     <row r="31" spans="1:11" ht="15.75" thickBot="1">
       <c r="A31" s="69" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B31" s="69" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C31" s="70">
         <v>0.5</v>
@@ -36623,10 +36613,10 @@
     </row>
     <row r="32" spans="1:11" ht="15.75" thickBot="1">
       <c r="A32" s="76" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B32" s="76" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C32" s="74">
         <v>0.3</v>
@@ -36658,10 +36648,10 @@
     </row>
     <row r="33" spans="1:11" ht="15.75" thickBot="1">
       <c r="A33" s="86" t="s">
+        <v>343</v>
+      </c>
+      <c r="B33" s="86" t="s">
         <v>345</v>
-      </c>
-      <c r="B33" s="86" t="s">
-        <v>347</v>
       </c>
       <c r="C33" s="87">
         <v>0.5</v>
@@ -36693,10 +36683,10 @@
     </row>
     <row r="34" spans="1:11" ht="15.75" thickBot="1">
       <c r="A34" s="66" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B34" s="66" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C34" s="67">
         <v>0.4</v>
@@ -36728,10 +36718,10 @@
     </row>
     <row r="35" spans="1:11" ht="15.75" thickBot="1">
       <c r="A35" s="85" t="s">
+        <v>346</v>
+      </c>
+      <c r="B35" s="85" t="s">
         <v>348</v>
-      </c>
-      <c r="B35" s="85" t="s">
-        <v>350</v>
       </c>
       <c r="C35" s="79">
         <v>0.01</v>
@@ -36763,10 +36753,10 @@
     </row>
     <row r="36" spans="1:11" ht="15.75" thickBot="1">
       <c r="A36" s="89" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B36" s="89" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C36" s="83">
         <v>0.3</v>
@@ -36798,10 +36788,10 @@
     </row>
     <row r="37" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A37" s="76" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B37" s="76" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C37" s="74">
         <v>0.4</v>
@@ -36833,10 +36823,10 @@
     </row>
     <row r="38" spans="1:11" ht="15.75" thickBot="1">
       <c r="A38" s="66" t="s">
+        <v>350</v>
+      </c>
+      <c r="B38" s="66" t="s">
         <v>352</v>
-      </c>
-      <c r="B38" s="66" t="s">
-        <v>354</v>
       </c>
       <c r="C38" s="67">
         <v>0.55000000000000004</v>
@@ -36868,10 +36858,10 @@
     </row>
     <row r="39" spans="1:11" ht="15.75" thickBot="1">
       <c r="A39" s="85" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B39" s="85" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C39" s="79">
         <v>0.25</v>
@@ -36903,10 +36893,10 @@
     </row>
     <row r="40" spans="1:11" ht="15.75" thickBot="1">
       <c r="A40" s="66" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B40" s="66" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C40" s="67">
         <v>0.3</v>
@@ -36938,10 +36928,10 @@
     </row>
     <row r="41" spans="1:11" ht="15.75" thickBot="1">
       <c r="A41" s="69" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B41" s="69" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C41" s="70">
         <v>0.5</v>
@@ -36973,10 +36963,10 @@
     </row>
     <row r="42" spans="1:11" ht="15.75" thickBot="1">
       <c r="A42" s="76" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B42" s="76" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C42" s="74">
         <v>0.7</v>
@@ -37008,10 +36998,10 @@
     </row>
     <row r="43" spans="1:11" ht="15.75" thickBot="1">
       <c r="A43" s="66" t="s">
+        <v>356</v>
+      </c>
+      <c r="B43" s="66" t="s">
         <v>358</v>
-      </c>
-      <c r="B43" s="66" t="s">
-        <v>360</v>
       </c>
       <c r="C43" s="67">
         <v>0</v>
@@ -37043,10 +37033,10 @@
     </row>
     <row r="44" spans="1:11" ht="15.75" thickBot="1">
       <c r="A44" s="85" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B44" s="85" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C44" s="79">
         <v>0.25</v>
@@ -37078,10 +37068,10 @@
     </row>
     <row r="45" spans="1:11" ht="15.75" thickBot="1">
       <c r="A45" s="66" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B45" s="66" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C45" s="67">
         <v>0.3</v>
@@ -37113,10 +37103,10 @@
     </row>
     <row r="46" spans="1:11" ht="15.75" thickBot="1">
       <c r="A46" s="90" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B46" s="90" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C46" s="91">
         <v>0.5</v>
@@ -37148,10 +37138,10 @@
     </row>
     <row r="47" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A47" s="72" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B47" s="72" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C47" s="74">
         <v>0.95</v>
@@ -37183,10 +37173,10 @@
     </row>
     <row r="48" spans="1:11" ht="15.75" thickBot="1">
       <c r="A48" s="93" t="s">
+        <v>359</v>
+      </c>
+      <c r="B48" s="93" t="s">
         <v>361</v>
-      </c>
-      <c r="B48" s="93" t="s">
-        <v>363</v>
       </c>
       <c r="C48" s="87">
         <v>0.15</v>
@@ -37218,10 +37208,10 @@
     </row>
     <row r="49" spans="1:11" ht="15.75" thickBot="1">
       <c r="A49" s="94" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B49" s="94" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C49" s="67">
         <v>0.6</v>
@@ -37253,10 +37243,10 @@
     </row>
     <row r="50" spans="1:11" ht="15.75" thickBot="1">
       <c r="A50" s="77" t="s">
+        <v>362</v>
+      </c>
+      <c r="B50" s="77" t="s">
         <v>364</v>
-      </c>
-      <c r="B50" s="77" t="s">
-        <v>366</v>
       </c>
       <c r="C50" s="79">
         <v>0.7</v>
@@ -37288,10 +37278,10 @@
     </row>
     <row r="51" spans="1:11" ht="15.75" thickBot="1">
       <c r="A51" s="94" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B51" s="94" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C51" s="67">
         <v>0.7</v>
@@ -37323,10 +37313,10 @@
     </row>
     <row r="52" spans="1:11" ht="15.75" thickBot="1">
       <c r="A52" s="95" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B52" s="95" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C52" s="70">
         <v>0.7</v>
@@ -37358,10 +37348,10 @@
     </row>
     <row r="53" spans="1:11" ht="15.75" thickBot="1">
       <c r="A53" s="72" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B53" s="72" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C53" s="74">
         <v>0.1</v>
@@ -37393,10 +37383,10 @@
     </row>
     <row r="54" spans="1:11" ht="15.75" thickBot="1">
       <c r="A54" s="94" t="s">
+        <v>367</v>
+      </c>
+      <c r="B54" s="94" t="s">
         <v>369</v>
-      </c>
-      <c r="B54" s="94" t="s">
-        <v>371</v>
       </c>
       <c r="C54" s="67">
         <v>0.4</v>
@@ -37428,10 +37418,10 @@
     </row>
     <row r="55" spans="1:11" ht="15.75" thickBot="1">
       <c r="A55" s="77" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B55" s="77" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C55" s="79">
         <v>0.75</v>
@@ -37463,10 +37453,10 @@
     </row>
     <row r="56" spans="1:11" ht="15.75" thickBot="1">
       <c r="A56" s="94" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B56" s="94" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C56" s="67">
         <v>0.7</v>
@@ -37498,10 +37488,10 @@
     </row>
     <row r="57" spans="1:11" ht="15.75" thickBot="1">
       <c r="A57" s="95" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B57" s="95" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C57" s="70">
         <v>0.65</v>
@@ -37533,10 +37523,10 @@
     </row>
     <row r="58" spans="1:11" ht="15.75" thickBot="1">
       <c r="A58" s="72" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B58" s="72" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C58" s="74">
         <v>0.1</v>
@@ -37568,10 +37558,10 @@
     </row>
     <row r="59" spans="1:11" ht="15.75" thickBot="1">
       <c r="A59" s="94" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B59" s="94" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C59" s="67">
         <v>0.4</v>
@@ -37603,10 +37593,10 @@
     </row>
     <row r="60" spans="1:11" ht="15.75" thickBot="1">
       <c r="A60" s="77" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B60" s="77" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C60" s="79">
         <v>0.75</v>
@@ -37638,10 +37628,10 @@
     </row>
     <row r="61" spans="1:11" ht="15.75" thickBot="1">
       <c r="A61" s="94" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B61" s="94" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C61" s="67">
         <v>0.7</v>
@@ -37673,10 +37663,10 @@
     </row>
     <row r="62" spans="1:11" ht="15.75" thickBot="1">
       <c r="A62" s="95" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B62" s="95" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C62" s="70">
         <v>0.65</v>
@@ -37708,10 +37698,10 @@
     </row>
     <row r="63" spans="1:11" ht="15.75" thickBot="1">
       <c r="A63" s="72" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B63" s="72" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C63" s="74">
         <v>0.1</v>
@@ -37743,10 +37733,10 @@
     </row>
     <row r="64" spans="1:11" ht="15.75" thickBot="1">
       <c r="A64" s="94" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B64" s="94" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C64" s="67">
         <v>0.4</v>
@@ -37778,10 +37768,10 @@
     </row>
     <row r="65" spans="1:11" ht="15.75" thickBot="1">
       <c r="A65" s="77" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B65" s="77" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C65" s="79">
         <v>0.75</v>
@@ -37813,10 +37803,10 @@
     </row>
     <row r="66" spans="1:11" ht="15.75" thickBot="1">
       <c r="A66" s="94" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B66" s="94" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C66" s="67">
         <v>0.7</v>
@@ -37848,10 +37838,10 @@
     </row>
     <row r="67" spans="1:11" ht="15.75" thickBot="1">
       <c r="A67" s="96" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B67" s="96" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C67" s="91">
         <v>0.65</v>
@@ -37883,10 +37873,10 @@
     </row>
     <row r="68" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A68" s="76" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B68" s="76" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C68" s="74">
         <v>0.2</v>
@@ -37918,10 +37908,10 @@
     </row>
     <row r="69" spans="1:11" ht="15.75" thickBot="1">
       <c r="A69" s="99" t="s">
+        <v>376</v>
+      </c>
+      <c r="B69" s="99" t="s">
         <v>378</v>
-      </c>
-      <c r="B69" s="99" t="s">
-        <v>380</v>
       </c>
       <c r="C69" s="100">
         <v>0.2</v>
@@ -37953,10 +37943,10 @@
     </row>
     <row r="70" spans="1:11" ht="15.75" thickBot="1">
       <c r="A70" s="85" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B70" s="85" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C70" s="79">
         <v>0.05</v>
@@ -37988,10 +37978,10 @@
     </row>
     <row r="71" spans="1:11" ht="15.75" thickBot="1">
       <c r="A71" s="66" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B71" s="66" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C71" s="67">
         <v>0.85</v>
@@ -38023,10 +38013,10 @@
     </row>
     <row r="72" spans="1:11" ht="15.75" thickBot="1">
       <c r="A72" s="85" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B72" s="85" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C72" s="79">
         <v>0.85</v>
@@ -38058,10 +38048,10 @@
     </row>
     <row r="73" spans="1:11" ht="15.75" thickBot="1">
       <c r="A73" s="86" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B73" s="86" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C73" s="87">
         <v>0.85</v>
@@ -38093,10 +38083,10 @@
     </row>
     <row r="74" spans="1:11" ht="15.75" thickBot="1">
       <c r="A74" s="66" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B74" s="66" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C74" s="67">
         <v>0.5</v>
@@ -38128,10 +38118,10 @@
     </row>
     <row r="75" spans="1:11" ht="15.75" thickBot="1">
       <c r="A75" s="85" t="s">
+        <v>383</v>
+      </c>
+      <c r="B75" s="85" t="s">
         <v>385</v>
-      </c>
-      <c r="B75" s="85" t="s">
-        <v>387</v>
       </c>
       <c r="C75" s="79">
         <v>0.7</v>
@@ -38163,10 +38153,10 @@
     </row>
     <row r="76" spans="1:11" ht="15.75" thickBot="1">
       <c r="A76" s="66" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B76" s="66" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C76" s="67">
         <v>0.65</v>
@@ -38198,10 +38188,10 @@
     </row>
     <row r="77" spans="1:11" ht="15.75" thickBot="1">
       <c r="A77" s="85" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B77" s="85" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C77" s="79">
         <v>0.65</v>
@@ -38233,10 +38223,10 @@
     </row>
     <row r="78" spans="1:11" ht="15.75" thickBot="1">
       <c r="A78" s="66" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B78" s="66" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C78" s="67">
         <v>0.7</v>
@@ -38268,10 +38258,10 @@
     </row>
     <row r="79" spans="1:11" ht="15.75" thickBot="1">
       <c r="A79" s="85" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B79" s="85" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C79" s="79">
         <v>0.55000000000000004</v>
@@ -38303,10 +38293,10 @@
     </row>
     <row r="80" spans="1:11" ht="15.75" thickBot="1">
       <c r="A80" s="86" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B80" s="86" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C80" s="87">
         <v>0.55000000000000004</v>
@@ -38338,10 +38328,10 @@
     </row>
     <row r="81" spans="1:11" ht="15.75" thickBot="1">
       <c r="A81" s="66" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B81" s="66" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="C81" s="67">
         <v>0.9</v>
@@ -38373,10 +38363,10 @@
     </row>
     <row r="82" spans="1:11" ht="15.75" thickBot="1">
       <c r="A82" s="85" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B82" s="85" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C82" s="79">
         <v>0.8</v>
@@ -38408,10 +38398,10 @@
     </row>
     <row r="83" spans="1:11" ht="15.75" thickBot="1">
       <c r="A83" s="86" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B83" s="86" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="C83" s="87">
         <v>0.7</v>
@@ -38443,10 +38433,10 @@
     </row>
     <row r="84" spans="1:11" ht="15.75" thickBot="1">
       <c r="A84" s="66" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B84" s="66" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C84" s="67">
         <v>0.5</v>
@@ -38478,10 +38468,10 @@
     </row>
     <row r="85" spans="1:11" ht="15.75" thickBot="1">
       <c r="A85" s="69" t="s">
+        <v>392</v>
+      </c>
+      <c r="B85" s="69" t="s">
         <v>394</v>
-      </c>
-      <c r="B85" s="69" t="s">
-        <v>396</v>
       </c>
       <c r="C85" s="70">
         <v>0.5</v>
@@ -38513,10 +38503,10 @@
     </row>
     <row r="86" spans="1:11" ht="15.75" thickBot="1">
       <c r="A86" s="76" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B86" s="76" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C86" s="74">
         <v>0.55000000000000004</v>
@@ -38548,10 +38538,10 @@
     </row>
     <row r="87" spans="1:11" ht="15.75" thickBot="1">
       <c r="A87" s="66" t="s">
+        <v>395</v>
+      </c>
+      <c r="B87" s="66" t="s">
         <v>397</v>
-      </c>
-      <c r="B87" s="66" t="s">
-        <v>399</v>
       </c>
       <c r="C87" s="67">
         <v>0.55000000000000004</v>
@@ -38583,10 +38573,10 @@
     </row>
     <row r="88" spans="1:11" ht="15.75" thickBot="1">
       <c r="A88" s="85" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B88" s="85" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C88" s="79">
         <v>0.55000000000000004</v>
@@ -38618,10 +38608,10 @@
     </row>
     <row r="89" spans="1:11" ht="15.75" thickBot="1">
       <c r="A89" s="66" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B89" s="66" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C89" s="67">
         <v>0.55000000000000004</v>
@@ -38653,10 +38643,10 @@
     </row>
     <row r="90" spans="1:11" ht="15.75" thickBot="1">
       <c r="A90" s="85" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B90" s="85" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="C90" s="79">
         <v>0.55000000000000004</v>
@@ -38688,10 +38678,10 @@
     </row>
     <row r="91" spans="1:11" ht="15.75" thickBot="1">
       <c r="A91" s="89" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B91" s="89" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C91" s="83">
         <v>0.3</v>
@@ -38723,10 +38713,10 @@
     </row>
     <row r="92" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A92" s="72" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B92" s="72" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C92" s="74">
         <v>0.3</v>
@@ -38758,10 +38748,10 @@
     </row>
     <row r="93" spans="1:11" ht="15.75" thickBot="1">
       <c r="A93" s="94" t="s">
+        <v>402</v>
+      </c>
+      <c r="B93" s="94" t="s">
         <v>404</v>
-      </c>
-      <c r="B93" s="94" t="s">
-        <v>406</v>
       </c>
       <c r="C93" s="67">
         <v>0.3</v>
@@ -38793,10 +38783,10 @@
     </row>
     <row r="94" spans="1:11" ht="15.75" thickBot="1">
       <c r="A94" s="77" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B94" s="77" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C94" s="79">
         <v>0.5</v>
@@ -38828,10 +38818,10 @@
     </row>
     <row r="95" spans="1:11" ht="15.75" thickBot="1">
       <c r="A95" s="94" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B95" s="94" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C95" s="67">
         <v>0.5</v>
@@ -38863,10 +38853,10 @@
     </row>
     <row r="96" spans="1:11" ht="15.75" thickBot="1">
       <c r="A96" s="77" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B96" s="77" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C96" s="79">
         <v>0.8</v>
@@ -38898,10 +38888,10 @@
     </row>
     <row r="97" spans="1:11" ht="15.75" thickBot="1">
       <c r="A97" s="94" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B97" s="94" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C97" s="67">
         <v>0.95</v>
@@ -38933,10 +38923,10 @@
     </row>
     <row r="98" spans="1:11" ht="15.75" thickBot="1">
       <c r="A98" s="77" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B98" s="77" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C98" s="79">
         <v>0.95</v>
@@ -38968,10 +38958,10 @@
     </row>
     <row r="99" spans="1:11" ht="15.75" thickBot="1">
       <c r="A99" s="94" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B99" s="94" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C99" s="67">
         <v>0.95</v>
@@ -39003,10 +38993,10 @@
     </row>
     <row r="100" spans="1:11" ht="15.75" thickBot="1">
       <c r="A100" s="77" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B100" s="77" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="C100" s="79">
         <v>0.95</v>
@@ -39038,10 +39028,10 @@
     </row>
     <row r="101" spans="1:11" ht="15.75" thickBot="1">
       <c r="A101" s="94" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B101" s="94" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C101" s="67">
         <v>0.8</v>
@@ -39073,10 +39063,10 @@
     </row>
     <row r="102" spans="1:11" ht="15.75" thickBot="1">
       <c r="A102" s="77" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B102" s="77" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="C102" s="79">
         <v>0.7</v>
@@ -39108,10 +39098,10 @@
     </row>
     <row r="103" spans="1:11" ht="15.75" thickBot="1">
       <c r="A103" s="94" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B103" s="94" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="C103" s="67">
         <v>0.75</v>
@@ -39143,10 +39133,10 @@
     </row>
     <row r="104" spans="1:11" ht="15.75" thickBot="1">
       <c r="A104" s="77" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B104" s="77" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C104" s="79">
         <v>0</v>
@@ -39178,10 +39168,10 @@
     </row>
     <row r="105" spans="1:11" ht="15.75" thickBot="1">
       <c r="A105" s="94" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B105" s="94" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="C105" s="67">
         <v>0.9</v>
@@ -39213,10 +39203,10 @@
     </row>
     <row r="106" spans="1:11" ht="15.75" thickBot="1">
       <c r="A106" s="77" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B106" s="77" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C106" s="79">
         <v>0.49</v>
@@ -39248,10 +39238,10 @@
     </row>
     <row r="107" spans="1:11" ht="15.75" thickBot="1">
       <c r="A107" s="94" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B107" s="94" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C107" s="67">
         <v>0</v>
@@ -39283,10 +39273,10 @@
     </row>
     <row r="108" spans="1:11" ht="15.75" thickBot="1">
       <c r="A108" s="95" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B108" s="95" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C108" s="70">
         <v>0.03</v>
@@ -39318,10 +39308,10 @@
     </row>
     <row r="109" spans="1:11" ht="15.75" thickBot="1">
       <c r="A109" s="72" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B109" s="72" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C109" s="74">
         <v>0.43</v>
@@ -39353,10 +39343,10 @@
     </row>
     <row r="110" spans="1:11" ht="15.75" thickBot="1">
       <c r="A110" s="94" t="s">
+        <v>420</v>
+      </c>
+      <c r="B110" s="94" t="s">
         <v>422</v>
-      </c>
-      <c r="B110" s="94" t="s">
-        <v>424</v>
       </c>
       <c r="C110" s="67">
         <v>0.8</v>
@@ -39388,10 +39378,10 @@
     </row>
     <row r="111" spans="1:11" ht="15.75" thickBot="1">
       <c r="A111" s="77" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B111" s="77" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C111" s="79">
         <v>0.3</v>
@@ -39423,10 +39413,10 @@
     </row>
     <row r="112" spans="1:11" ht="15.75" thickBot="1">
       <c r="A112" s="94" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B112" s="94" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C112" s="112">
         <v>0.7</v>
@@ -39458,10 +39448,10 @@
     </row>
     <row r="113" spans="1:11" ht="15.75" thickBot="1">
       <c r="A113" s="77" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B113" s="77" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="C113" s="79">
         <v>0.5</v>
@@ -39493,10 +39483,10 @@
     </row>
     <row r="114" spans="1:11" ht="15.75" thickBot="1">
       <c r="A114" s="113" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B114" s="113" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C114" s="114">
         <v>0.4</v>
@@ -39528,10 +39518,10 @@
     </row>
     <row r="115" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A115" s="86" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B115" s="86" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C115" s="87">
         <v>0.1</v>
@@ -39563,10 +39553,10 @@
     </row>
     <row r="116" spans="1:11" ht="15.75" thickBot="1">
       <c r="A116" s="86" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B116" s="86" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C116" s="87">
         <v>0.1</v>
@@ -39598,10 +39588,10 @@
     </row>
     <row r="117" spans="1:11" ht="15.75" thickBot="1">
       <c r="A117" s="76" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B117" s="76" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="C117" s="74">
         <v>0</v>
@@ -39633,10 +39623,10 @@
     </row>
     <row r="118" spans="1:11" ht="15.75" thickBot="1">
       <c r="A118" s="66" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B118" s="66" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C118" s="67">
         <v>0</v>
@@ -39668,10 +39658,10 @@
     </row>
     <row r="119" spans="1:11" ht="15.75" thickBot="1">
       <c r="A119" s="90" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B119" s="90" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="C119" s="91">
         <v>0</v>
@@ -39703,10 +39693,10 @@
     </row>
     <row r="120" spans="1:11" ht="16.5" thickTop="1" thickBot="1">
       <c r="A120" s="86" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B120" s="86" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C120" s="87">
         <v>0.15</v>
@@ -39738,10 +39728,10 @@
     </row>
     <row r="121" spans="1:11">
       <c r="A121" s="66" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B121" s="116" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C121" s="67">
         <v>0</v>
@@ -39773,10 +39763,10 @@
     </row>
     <row r="122" spans="1:11" ht="15.75" thickBot="1">
       <c r="A122" s="86" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B122" s="117" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="C122" s="87">
         <v>0</v>
@@ -39808,10 +39798,10 @@
     </row>
     <row r="123" spans="1:11" ht="15.75" thickBot="1">
       <c r="A123" s="86" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B123" s="86" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C123" s="87">
         <v>0</v>
@@ -39843,10 +39833,10 @@
     </row>
     <row r="124" spans="1:11" ht="15.75" thickBot="1">
       <c r="A124" s="89" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B124" s="89" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C124" s="83">
         <v>0</v>
@@ -39878,10 +39868,10 @@
     </row>
     <row r="125" spans="1:11" ht="15.75" thickTop="1">
       <c r="A125" s="118" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B125" s="118" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C125" s="119">
         <v>0.01</v>
@@ -39913,10 +39903,10 @@
     </row>
     <row r="126" spans="1:11" ht="15.75" thickBot="1">
       <c r="A126" s="121" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B126" s="121" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C126" s="122">
         <v>0</v>
@@ -39948,10 +39938,10 @@
     </row>
     <row r="127" spans="1:11">
       <c r="A127" s="124" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B127" s="124" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C127" s="125">
         <v>0.01</v>
@@ -39983,10 +39973,10 @@
     </row>
     <row r="128" spans="1:11" ht="15.75" thickBot="1">
       <c r="A128" s="127" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B128" s="127" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C128" s="128">
         <v>0</v>
@@ -40018,10 +40008,10 @@
     </row>
     <row r="129" spans="1:11" ht="15.75" thickTop="1">
       <c r="A129" s="94" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B129" s="94" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="C129" s="112">
         <v>0</v>
@@ -40053,10 +40043,10 @@
     </row>
     <row r="130" spans="1:11">
       <c r="A130" s="94" t="s">
+        <v>439</v>
+      </c>
+      <c r="B130" s="130" t="s">
         <v>441</v>
-      </c>
-      <c r="B130" s="130" t="s">
-        <v>443</v>
       </c>
       <c r="C130" s="112">
         <v>0</v>
@@ -40088,10 +40078,10 @@
     </row>
     <row r="131" spans="1:11" ht="15.75" thickBot="1">
       <c r="A131" s="93" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="B131" s="131" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C131" s="132">
         <v>0</v>
@@ -40123,10 +40113,10 @@
     </row>
     <row r="132" spans="1:11">
       <c r="A132" s="94" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B132" s="94" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="C132" s="112">
         <v>0</v>
@@ -40158,10 +40148,10 @@
     </row>
     <row r="133" spans="1:11">
       <c r="A133" s="94" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B133" s="94" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C133" s="112">
         <v>0</v>
@@ -40193,10 +40183,10 @@
     </row>
     <row r="134" spans="1:11">
       <c r="A134" s="94" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B134" s="130" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C134" s="112">
         <v>0</v>
@@ -40228,10 +40218,10 @@
     </row>
     <row r="135" spans="1:11" ht="15.75" thickBot="1">
       <c r="A135" s="93" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B135" s="131" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C135" s="132">
         <v>0</v>
@@ -40263,10 +40253,10 @@
     </row>
     <row r="136" spans="1:11">
       <c r="A136" s="94" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B136" s="94" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="C136" s="112">
         <v>0</v>
@@ -40298,10 +40288,10 @@
     </row>
     <row r="137" spans="1:11">
       <c r="A137" s="94" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B137" s="130" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C137" s="112">
         <v>0</v>
@@ -40333,10 +40323,10 @@
     </row>
     <row r="138" spans="1:11" ht="15.75" thickBot="1">
       <c r="A138" s="93" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B138" s="131" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C138" s="132">
         <v>0</v>
@@ -40368,10 +40358,10 @@
     </row>
     <row r="139" spans="1:11">
       <c r="A139" s="94" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B139" s="94" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C139" s="112">
         <v>0</v>
@@ -40403,10 +40393,10 @@
     </row>
     <row r="140" spans="1:11">
       <c r="A140" s="94" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B140" s="94" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C140" s="112">
         <v>0</v>
@@ -40438,10 +40428,10 @@
     </row>
     <row r="141" spans="1:11">
       <c r="A141" s="94" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B141" s="130" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C141" s="112">
         <v>0</v>
@@ -40473,10 +40463,10 @@
     </row>
     <row r="142" spans="1:11">
       <c r="A142" s="94" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B142" s="130" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C142" s="112">
         <v>0</v>
@@ -40508,10 +40498,10 @@
     </row>
     <row r="143" spans="1:11">
       <c r="A143" s="94" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B143" s="94" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C143" s="112">
         <v>0</v>
@@ -40543,10 +40533,10 @@
     </row>
     <row r="144" spans="1:11" ht="15.75" thickBot="1">
       <c r="A144" s="93" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="B144" s="131" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C144" s="132">
         <v>0</v>
@@ -40578,10 +40568,10 @@
     </row>
     <row r="145" spans="1:11">
       <c r="A145" s="94" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B145" s="94" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="C145" s="112">
         <v>0</v>
@@ -40613,10 +40603,10 @@
     </row>
     <row r="146" spans="1:11">
       <c r="A146" s="94" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B146" s="94" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C146" s="112">
         <v>0</v>
@@ -40648,10 +40638,10 @@
     </row>
     <row r="147" spans="1:11">
       <c r="A147" s="94" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B147" s="130" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C147" s="112">
         <v>0</v>
@@ -40683,10 +40673,10 @@
     </row>
     <row r="148" spans="1:11">
       <c r="A148" s="94" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B148" s="130" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C148" s="112">
         <v>0</v>
@@ -40718,10 +40708,10 @@
     </row>
     <row r="149" spans="1:11">
       <c r="A149" s="94" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B149" s="94" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C149" s="112">
         <v>0</v>
@@ -40753,10 +40743,10 @@
     </row>
     <row r="150" spans="1:11">
       <c r="A150" s="94" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B150" s="130" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C150" s="112">
         <v>0</v>
@@ -40788,10 +40778,10 @@
     </row>
     <row r="151" spans="1:11" ht="15.75" thickBot="1">
       <c r="A151" s="93" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="B151" s="93" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="C151" s="132">
         <v>0</v>
@@ -40823,10 +40813,10 @@
     </row>
     <row r="152" spans="1:11">
       <c r="A152" s="94" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B152" s="94" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="C152" s="112">
         <v>0</v>
@@ -40858,10 +40848,10 @@
     </row>
     <row r="153" spans="1:11">
       <c r="A153" s="94" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B153" s="130" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C153" s="112">
         <v>0</v>
@@ -40893,10 +40883,10 @@
     </row>
     <row r="154" spans="1:11">
       <c r="A154" s="94" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B154" s="130" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C154" s="112">
         <v>0</v>
@@ -40928,10 +40918,10 @@
     </row>
     <row r="155" spans="1:11">
       <c r="A155" s="94" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B155" s="94" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C155" s="112">
         <v>0</v>
@@ -40963,10 +40953,10 @@
     </row>
     <row r="156" spans="1:11" ht="15.75" thickBot="1">
       <c r="A156" s="81" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="B156" s="134" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C156" s="82">
         <v>0</v>
@@ -40998,10 +40988,10 @@
     </row>
     <row r="157" spans="1:11" ht="15.75" thickTop="1">
       <c r="A157" s="66" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B157" s="66" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="C157" s="67">
         <v>0</v>
@@ -41033,10 +41023,10 @@
     </row>
     <row r="158" spans="1:11" ht="15.75" thickBot="1">
       <c r="A158" s="93" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B158" s="93" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="C158" s="87">
         <v>0</v>
@@ -41068,10 +41058,10 @@
     </row>
     <row r="159" spans="1:11" ht="15.75" thickBot="1">
       <c r="A159" s="81" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B159" s="81" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C159" s="83">
         <v>0</v>
@@ -41103,10 +41093,10 @@
     </row>
     <row r="160" spans="1:11" ht="15.75" thickTop="1">
       <c r="A160" s="94" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B160" s="94" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="C160" s="112">
         <v>0</v>
@@ -41138,10 +41128,10 @@
     </row>
     <row r="161" spans="1:11">
       <c r="A161" s="94" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B161" s="130" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C161" s="112">
         <v>0</v>
@@ -41173,10 +41163,10 @@
     </row>
     <row r="162" spans="1:11">
       <c r="A162" s="94" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B162" s="130" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C162" s="112">
         <v>0</v>
@@ -41208,10 +41198,10 @@
     </row>
     <row r="163" spans="1:11" ht="15.75" thickBot="1">
       <c r="A163" s="93" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B163" s="131" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C163" s="132">
         <v>0</v>
@@ -41243,10 +41233,10 @@
     </row>
     <row r="164" spans="1:11">
       <c r="A164" s="94" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B164" s="94" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="C164" s="112">
         <v>0</v>
@@ -41278,10 +41268,10 @@
     </row>
     <row r="165" spans="1:11">
       <c r="A165" s="94" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B165" s="130" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C165" s="112">
         <v>0</v>
@@ -41313,10 +41303,10 @@
     </row>
     <row r="166" spans="1:11">
       <c r="A166" s="94" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B166" s="130" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C166" s="112">
         <v>0</v>
@@ -41348,10 +41338,10 @@
     </row>
     <row r="167" spans="1:11">
       <c r="A167" s="94" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B167" s="130" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C167" s="112">
         <v>0</v>
@@ -41383,10 +41373,10 @@
     </row>
     <row r="168" spans="1:11" ht="15.75" thickBot="1">
       <c r="A168" s="138" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B168" s="138" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C168" s="139">
         <v>0</v>
@@ -41418,10 +41408,10 @@
     </row>
     <row r="169" spans="1:11">
       <c r="A169" s="94" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B169" s="130" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C169" s="112">
         <v>0</v>
@@ -41453,10 +41443,10 @@
     </row>
     <row r="170" spans="1:11">
       <c r="A170" s="94" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B170" s="130" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C170" s="112">
         <v>0</v>
@@ -41488,10 +41478,10 @@
     </row>
     <row r="171" spans="1:11" ht="15.75" thickBot="1">
       <c r="A171" s="93" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B171" s="131" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="C171" s="132">
         <v>0</v>
@@ -41523,10 +41513,10 @@
     </row>
     <row r="172" spans="1:11">
       <c r="A172" s="94" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B172" s="130" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="C172" s="112">
         <v>0</v>
@@ -41558,10 +41548,10 @@
     </row>
     <row r="173" spans="1:11">
       <c r="A173" s="94" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B173" s="130" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C173" s="112">
         <v>0</v>
@@ -41593,10 +41583,10 @@
     </row>
     <row r="174" spans="1:11">
       <c r="A174" s="94" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B174" s="94" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C174" s="112">
         <v>0</v>
@@ -41628,10 +41618,10 @@
     </row>
     <row r="175" spans="1:11" ht="15.75" thickBot="1">
       <c r="A175" s="93" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B175" s="131" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C175" s="132">
         <v>0</v>
@@ -41685,64 +41675,64 @@
     <row r="1" spans="2:14" ht="15.75" thickBot="1"/>
     <row r="2" spans="2:14" ht="30.95" customHeight="1">
       <c r="D2" s="142" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="E2" s="142"/>
       <c r="F2" s="142"/>
       <c r="G2" s="142"/>
       <c r="H2" s="142"/>
-      <c r="I2" s="195" t="s">
-        <v>506</v>
-      </c>
-      <c r="J2" s="196"/>
-      <c r="K2" s="196"/>
-      <c r="L2" s="196"/>
-      <c r="M2" s="197"/>
+      <c r="I2" s="201" t="s">
+        <v>504</v>
+      </c>
+      <c r="J2" s="202"/>
+      <c r="K2" s="202"/>
+      <c r="L2" s="202"/>
+      <c r="M2" s="203"/>
     </row>
     <row r="3" spans="2:14" ht="60">
       <c r="B3" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C3" s="9" t="s">
+        <v>496</v>
+      </c>
+      <c r="D3" s="143" t="s">
         <v>498</v>
       </c>
-      <c r="D3" s="143" t="s">
+      <c r="E3" s="143" t="s">
+        <v>499</v>
+      </c>
+      <c r="F3" s="143" t="s">
         <v>500</v>
       </c>
-      <c r="E3" s="143" t="s">
+      <c r="G3" s="143" t="s">
         <v>501</v>
       </c>
-      <c r="F3" s="143" t="s">
+      <c r="H3" s="147" t="s">
         <v>502</v>
       </c>
-      <c r="G3" s="143" t="s">
-        <v>503</v>
-      </c>
-      <c r="H3" s="147" t="s">
-        <v>504</v>
-      </c>
       <c r="I3" s="148" t="s">
+        <v>498</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="K3" s="9" t="s">
         <v>500</v>
       </c>
-      <c r="J3" s="9" t="s">
+      <c r="L3" s="9" t="s">
         <v>501</v>
       </c>
-      <c r="K3" s="9" t="s">
+      <c r="M3" s="149" t="s">
         <v>502</v>
       </c>
-      <c r="L3" s="9" t="s">
-        <v>503</v>
-      </c>
-      <c r="M3" s="149" t="s">
-        <v>504</v>
-      </c>
       <c r="N3" s="189" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
     </row>
     <row r="4" spans="2:14">
       <c r="B4" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C4" s="141">
         <v>4.1094089371344421E-2</v>
@@ -41788,7 +41778,7 @@
     </row>
     <row r="5" spans="2:14">
       <c r="B5" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C5" s="141">
         <v>0</v>
@@ -41834,7 +41824,7 @@
     </row>
     <row r="6" spans="2:14">
       <c r="B6" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C6" s="141">
         <v>4.0805825486475107E-2</v>
@@ -41880,7 +41870,7 @@
     </row>
     <row r="7" spans="2:14">
       <c r="B7" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="C7" s="141">
         <v>2.3082653003295327E-2</v>
@@ -41926,7 +41916,7 @@
     </row>
     <row r="8" spans="2:14">
       <c r="B8" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="C8" s="141">
         <v>9.7591784811817753E-2</v>
@@ -41972,7 +41962,7 @@
     </row>
     <row r="9" spans="2:14">
       <c r="B9" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="C9" s="141">
         <v>3.2056865699710202E-3</v>
@@ -42018,7 +42008,7 @@
     </row>
     <row r="10" spans="2:14">
       <c r="B10" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C10" s="141">
         <v>5.8503779901971122E-2</v>
@@ -42064,7 +42054,7 @@
     </row>
     <row r="11" spans="2:14">
       <c r="B11" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C11" s="141">
         <v>0.17093361928399475</v>
@@ -42110,7 +42100,7 @@
     </row>
     <row r="12" spans="2:14">
       <c r="B12" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C12" s="141">
         <v>0.10696307521803304</v>
@@ -42156,7 +42146,7 @@
     </row>
     <row r="13" spans="2:14">
       <c r="B13" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="C13" s="141">
         <v>0.24341846687979948</v>
@@ -42202,7 +42192,7 @@
     </row>
     <row r="14" spans="2:14">
       <c r="B14" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C14" s="141">
         <v>1.0578765680904366E-2</v>
@@ -42248,7 +42238,7 @@
     </row>
     <row r="15" spans="2:14">
       <c r="B15" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="C15" s="141">
         <v>1.4853014440865727E-2</v>
@@ -42294,7 +42284,7 @@
     </row>
     <row r="16" spans="2:14">
       <c r="B16" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C16" s="141">
         <v>4.5141623428579913E-2</v>
@@ -42340,7 +42330,7 @@
     </row>
     <row r="17" spans="2:14">
       <c r="B17" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="C17" s="141">
         <v>4.7764729892568206E-2</v>
@@ -42386,7 +42376,7 @@
     </row>
     <row r="18" spans="2:14">
       <c r="B18" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C18" s="141">
         <v>2.7782616939748844E-2</v>
@@ -42432,7 +42422,7 @@
     </row>
     <row r="19" spans="2:14">
       <c r="B19" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C19" s="141">
         <v>2.660719853075947E-2</v>
@@ -42478,7 +42468,7 @@
     </row>
     <row r="20" spans="2:14">
       <c r="B20" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C20" s="141">
         <v>2.030268160981646E-3</v>
@@ -42524,7 +42514,7 @@
     </row>
     <row r="21" spans="2:14">
       <c r="B21" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C21" s="141">
         <v>2.7782616939748843E-3</v>
@@ -42570,7 +42560,7 @@
     </row>
     <row r="22" spans="2:14">
       <c r="B22" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="C22" s="141">
         <v>3.3125427889700541E-3</v>
@@ -42616,7 +42606,7 @@
     </row>
     <row r="23" spans="2:14">
       <c r="B23" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C23" s="141">
         <v>3.2056865699710202E-3</v>
@@ -42662,7 +42652,7 @@
     </row>
     <row r="24" spans="2:14">
       <c r="B24" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="C24" s="141">
         <v>2.030268160981646E-3</v>
@@ -42708,7 +42698,7 @@
     </row>
     <row r="25" spans="2:14">
       <c r="B25" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C25" s="141">
         <v>4.4452187103598152E-3</v>
@@ -42754,7 +42744,7 @@
     </row>
     <row r="26" spans="2:14">
       <c r="B26" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C26" s="141">
         <v>0</v>
@@ -42800,7 +42790,7 @@
     </row>
     <row r="27" spans="2:14">
       <c r="B27" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C27" s="141">
         <v>6.4113731399420408E-4</v>
@@ -42846,7 +42836,7 @@
     </row>
     <row r="28" spans="2:14" ht="15.75" thickBot="1">
       <c r="B28" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="C28" s="141">
         <v>2.3229687160638002E-2</v>
@@ -42892,7 +42882,7 @@
     </row>
     <row r="29" spans="2:14">
       <c r="C29" s="2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
     </row>
   </sheetData>
@@ -42929,7 +42919,7 @@
   <sheetPr>
     <tabColor theme="3" tint="0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="45" bestFit="1" customWidth="1"/>
@@ -42941,19 +42931,19 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
+        <v>234</v>
+      </c>
+      <c r="C1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D1" t="s">
         <v>236</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>237</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>238</v>
-      </c>
-      <c r="E1" t="s">
-        <v>239</v>
-      </c>
-      <c r="F1" t="s">
-        <v>240</v>
       </c>
       <c r="G1" t="s">
         <v>20</v>
@@ -42965,13 +42955,13 @@
         <v>22</v>
       </c>
       <c r="J1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="K1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="L1" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="2" spans="1:12">
@@ -43105,11 +43095,11 @@
         <v>2.5</v>
       </c>
       <c r="I4" s="12">
-        <f t="shared" ref="I4:I13" si="0">I3</f>
+        <f t="shared" ref="I4:I11" si="0">I3</f>
         <v>1.639344262295082</v>
       </c>
       <c r="J4" s="12">
-        <f t="shared" ref="J4:J13" si="1">B4</f>
+        <f t="shared" ref="J4:J11" si="1">B4</f>
         <v>1.1764705882352942</v>
       </c>
       <c r="K4" s="12">
@@ -43162,11 +43152,11 @@
         <v>1.1490217356611665</v>
       </c>
       <c r="K5" s="12">
-        <f t="shared" ref="K5:K13" si="2">$K$3</f>
+        <f t="shared" ref="K5:K11" si="2">$K$3</f>
         <v>3.3492282122238457</v>
       </c>
       <c r="L5" s="12">
-        <f t="shared" ref="L5:L13" si="3">$L$3</f>
+        <f t="shared" ref="L5:L11" si="3">$L$3</f>
         <v>3.2788295116156565</v>
       </c>
     </row>
@@ -43464,119 +43454,21 @@
       </c>
     </row>
     <row r="12" spans="1:12">
-      <c r="A12" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" s="12">
-        <f>1/'Combustion Efficiency'!D105</f>
-        <v>1.1764705882352942</v>
-      </c>
-      <c r="C12" s="12">
-        <f>1/'Combustion Efficiency'!D106</f>
-        <v>1.2048192771084338</v>
-      </c>
-      <c r="D12" s="12">
-        <f>1/'Combustion Efficiency'!D107</f>
-        <v>1.3769693936950533</v>
-      </c>
-      <c r="E12" s="12">
-        <f>1/'Combustion Efficiency'!D108</f>
-        <v>1.7299035780390835</v>
-      </c>
-      <c r="F12" s="12">
-        <f>1/'Combustion Efficiency'!D109</f>
-        <v>2.0438738318980092</v>
-      </c>
-      <c r="G12" s="12">
-        <f>Cooling!$K$4</f>
-        <v>0.89743589743589736</v>
-      </c>
-      <c r="H12" s="12">
-        <f>'Machine Drive'!$J$36</f>
-        <v>2.5</v>
-      </c>
-      <c r="I12" s="12">
-        <f t="shared" si="0"/>
-        <v>1.639344262295082</v>
-      </c>
-      <c r="J12" s="12">
-        <f t="shared" si="1"/>
-        <v>1.1764705882352942</v>
-      </c>
-      <c r="K12" s="12">
-        <f t="shared" si="2"/>
-        <v>3.3492282122238457</v>
-      </c>
-      <c r="L12" s="12">
-        <f t="shared" si="3"/>
-        <v>3.2788295116156565</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12">
-      <c r="A13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B13" s="12">
-        <f>1/'Combustion Efficiency'!D105</f>
-        <v>1.1764705882352942</v>
-      </c>
-      <c r="C13" s="12">
-        <f>1/'Combustion Efficiency'!D106</f>
-        <v>1.2048192771084338</v>
-      </c>
-      <c r="D13" s="12">
-        <f>1/'Combustion Efficiency'!D107</f>
-        <v>1.3769693936950533</v>
-      </c>
-      <c r="E13" s="12">
-        <f>1/'Combustion Efficiency'!D108</f>
-        <v>1.7299035780390835</v>
-      </c>
-      <c r="F13" s="12">
-        <f>1/'Combustion Efficiency'!D109</f>
-        <v>2.0438738318980092</v>
-      </c>
-      <c r="G13" s="12">
-        <f>Cooling!$K$4</f>
-        <v>0.89743589743589736</v>
-      </c>
-      <c r="H13" s="12">
-        <f>'Machine Drive'!$J$36</f>
-        <v>2.5</v>
-      </c>
-      <c r="I13" s="12">
-        <f t="shared" si="0"/>
-        <v>1.639344262295082</v>
-      </c>
-      <c r="J13" s="12">
-        <f t="shared" si="1"/>
-        <v>1.1764705882352942</v>
-      </c>
-      <c r="K13" s="12">
-        <f t="shared" si="2"/>
-        <v>3.3492282122238457</v>
-      </c>
-      <c r="L13" s="12">
-        <f t="shared" si="3"/>
-        <v>3.2788295116156565</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12">
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3"/>
+      <c r="F12" s="3"/>
+      <c r="G12" s="3"/>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:F13">
-    <cfRule type="colorScale" priority="2">
+  <conditionalFormatting sqref="A1:F11">
+    <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -43587,8 +43479,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B2:F13">
-    <cfRule type="colorScale" priority="1">
+  <conditionalFormatting sqref="B2:F11">
+    <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -43618,15 +43510,15 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="18" spans="2:13">
       <c r="D18" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E18" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F18">
         <v>2018</v>
@@ -43635,27 +43527,27 @@
         <v>2050</v>
       </c>
       <c r="K18" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="19" spans="2:13">
       <c r="B19" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" t="s">
         <v>35</v>
       </c>
-      <c r="C19" t="s">
+      <c r="E19" t="s">
         <v>36</v>
       </c>
-      <c r="D19" t="s">
+      <c r="F19" t="s">
         <v>37</v>
       </c>
-      <c r="E19" t="s">
-        <v>38</v>
-      </c>
-      <c r="F19" t="s">
-        <v>39</v>
-      </c>
       <c r="G19" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="I19">
         <v>2021</v>
@@ -43664,18 +43556,18 @@
         <v>2050</v>
       </c>
       <c r="K19" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M19" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20" spans="2:13">
       <c r="B20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C20" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D20">
         <v>0.218</v>
@@ -43708,10 +43600,10 @@
     </row>
     <row r="21" spans="2:13">
       <c r="B21" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" t="s">
         <v>42</v>
-      </c>
-      <c r="C21" t="s">
-        <v>44</v>
       </c>
       <c r="D21">
         <v>2.1999999999999999E-2</v>
@@ -43744,10 +43636,10 @@
     </row>
     <row r="22" spans="2:13">
       <c r="B22" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C22" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D22">
         <v>0.20399999999999999</v>
@@ -43780,10 +43672,10 @@
     </row>
     <row r="23" spans="2:13">
       <c r="B23" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C23" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D23">
         <v>3.9E-2</v>
@@ -43816,10 +43708,10 @@
     </row>
     <row r="24" spans="2:13">
       <c r="B24" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C24" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D24">
         <v>1.2999999999999999E-2</v>
@@ -43852,10 +43744,10 @@
     </row>
     <row r="25" spans="2:13">
       <c r="B25" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C25" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D25">
         <v>0.19900000000000001</v>
@@ -43888,10 +43780,10 @@
     </row>
     <row r="26" spans="2:13">
       <c r="B26" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C26" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D26">
         <v>1E-3</v>
@@ -43924,10 +43816,10 @@
     </row>
     <row r="27" spans="2:13">
       <c r="B27" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C27" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D27">
         <v>1.0999999999999999E-2</v>
@@ -43960,10 +43852,10 @@
     </row>
     <row r="28" spans="2:13">
       <c r="B28" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C28" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D28">
         <v>7.0000000000000001E-3</v>
@@ -44016,39 +43908,39 @@
   <sheetData>
     <row r="2" spans="8:15">
       <c r="H2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="8:15">
       <c r="H3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="8:15" s="9" customFormat="1" ht="45">
       <c r="I4" s="9" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="J4" s="9" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="N4" s="9" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="8:15">
       <c r="L5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="8:15">
       <c r="I6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="J6">
         <v>83</v>
@@ -44057,7 +43949,7 @@
         <v>82</v>
       </c>
       <c r="L6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M6">
         <v>90.1</v>
@@ -44072,7 +43964,7 @@
     </row>
     <row r="7" spans="8:15">
       <c r="I7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="J7">
         <v>89</v>
@@ -44081,7 +43973,7 @@
         <v>89</v>
       </c>
       <c r="L7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="M7">
         <v>93.1</v>
@@ -44096,7 +43988,7 @@
     </row>
     <row r="8" spans="8:15">
       <c r="I8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J8">
         <v>92</v>
@@ -44105,7 +43997,7 @@
         <v>91</v>
       </c>
       <c r="L8" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="M8">
         <v>94.7</v>
@@ -44120,7 +44012,7 @@
     </row>
     <row r="9" spans="8:15">
       <c r="I9" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J9">
         <v>93</v>
@@ -44129,7 +44021,7 @@
         <v>92</v>
       </c>
       <c r="L9" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="M9">
         <v>95.9</v>
@@ -44144,7 +44036,7 @@
     </row>
     <row r="10" spans="8:15">
       <c r="I10" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J10">
         <v>93</v>
@@ -44153,7 +44045,7 @@
         <v>93</v>
       </c>
       <c r="L10" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="M10">
         <v>96.2</v>
@@ -44168,7 +44060,7 @@
     </row>
     <row r="11" spans="8:15">
       <c r="I11" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="J11">
         <v>93</v>
@@ -44177,7 +44069,7 @@
         <v>94</v>
       </c>
       <c r="L11" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="M11">
         <v>96.2</v>
@@ -44192,7 +44084,7 @@
     </row>
     <row r="12" spans="8:15">
       <c r="I12" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J12">
         <v>93</v>
@@ -44211,7 +44103,7 @@
     </row>
     <row r="13" spans="8:15">
       <c r="I13" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J13">
         <v>92</v>
@@ -44230,7 +44122,7 @@
     </row>
     <row r="14" spans="8:15">
       <c r="I14" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="J14">
         <v>86</v>
@@ -44249,13 +44141,13 @@
     </row>
     <row r="15" spans="8:15">
       <c r="I15" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="J15">
         <v>91</v>
       </c>
       <c r="K15" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="M15">
         <f>M14</f>
@@ -44268,23 +44160,23 @@
     </row>
     <row r="17" spans="9:12">
       <c r="J17" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18" spans="9:12">
       <c r="I18" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="J18" s="18">
         <v>25.980397752045299</v>
       </c>
       <c r="L18" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19" spans="9:12">
       <c r="I19" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="J19" s="18">
         <v>67.647063795395397</v>
@@ -44295,18 +44187,18 @@
     </row>
     <row r="20" spans="9:12">
       <c r="I20" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="J20" s="18">
         <v>86.928108261286297</v>
       </c>
       <c r="L20" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" spans="9:12">
       <c r="I21" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J21" s="18">
         <v>71.895427750300499</v>
@@ -44314,7 +44206,7 @@
     </row>
     <row r="22" spans="9:12">
       <c r="I22" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="J22" s="18">
         <v>64.379085998847998</v>
@@ -44322,7 +44214,7 @@
     </row>
     <row r="23" spans="9:12">
       <c r="I23" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="J23" s="18">
         <v>94.281049327759803</v>
@@ -44330,7 +44222,7 @@
     </row>
     <row r="24" spans="9:12">
       <c r="I24" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="J24" s="18">
         <v>62.908497785553301</v>
@@ -44338,7 +44230,7 @@
     </row>
     <row r="25" spans="9:12">
       <c r="I25" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="J25" s="18">
         <v>34.803927031813501</v>
@@ -44346,7 +44238,7 @@
     </row>
     <row r="26" spans="9:12">
       <c r="I26" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="J26" s="18">
         <v>17.6470525756977</v>
@@ -44354,7 +44246,7 @@
     </row>
     <row r="27" spans="9:12">
       <c r="I27" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="J27" s="18">
         <v>17.156856504599499</v>
@@ -44362,10 +44254,10 @@
     </row>
     <row r="29" spans="9:12">
       <c r="J29" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30" spans="9:12">
@@ -44390,7 +44282,7 @@
     </row>
     <row r="34" spans="10:11">
       <c r="J34" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="35" spans="10:11">
@@ -44418,21 +44310,21 @@
   <sheetData>
     <row r="24" spans="2:8">
       <c r="B24" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C24" s="32">
         <v>3.7</v>
       </c>
       <c r="D24" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="H24" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="25" spans="2:8">
       <c r="B25" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C25">
         <f>1/C24</f>
@@ -44444,18 +44336,18 @@
     </row>
     <row r="27" spans="2:8">
       <c r="B27" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C27">
         <v>3.5</v>
       </c>
       <c r="D27" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
     </row>
     <row r="28" spans="2:8">
       <c r="B28" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C28">
         <f>1/C27</f>
@@ -44464,18 +44356,18 @@
     </row>
     <row r="30" spans="2:8">
       <c r="B30" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="C30" s="33">
         <v>2.23</v>
       </c>
       <c r="D30" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="31" spans="2:8">
       <c r="B31" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C31" s="12">
         <f>IFERROR(1/C30,"")</f>
@@ -44496,7 +44388,7 @@
   <sheetData>
     <row r="2" spans="1:9">
       <c r="A2" s="22" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B2" s="21"/>
       <c r="C2" s="21"/>
@@ -44509,24 +44401,24 @@
     </row>
     <row r="3" spans="1:9">
       <c r="B3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="B4">
         <v>425</v>
       </c>
       <c r="C4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E4">
         <f>AVERAGE(B4:B6)</f>
@@ -44539,40 +44431,40 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B5">
         <v>440</v>
       </c>
       <c r="C5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B6">
         <v>400</v>
       </c>
       <c r="C6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="B7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B8">
         <v>361</v>
       </c>
       <c r="C8" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E8">
         <f>AVERAGE(B8:B10)</f>
@@ -44581,29 +44473,29 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B9">
         <v>350</v>
       </c>
       <c r="C9" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B10">
         <v>300</v>
       </c>
       <c r="C10" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="22" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B12" s="21"/>
       <c r="C12" s="21"/>
@@ -44616,23 +44508,23 @@
     </row>
     <row r="13" spans="1:9">
       <c r="B13" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B14" s="23">
         <v>0.504</v>
       </c>
       <c r="G14" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="B15" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="G15">
         <f>1/B14</f>
@@ -44641,7 +44533,7 @@
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B16" s="23">
         <v>0.55100000000000005</v>
@@ -44649,7 +44541,7 @@
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="22" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B18" s="22"/>
       <c r="C18" s="22"/>
@@ -44662,10 +44554,10 @@
     </row>
     <row r="19" spans="1:9">
       <c r="B19" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G19" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -44673,7 +44565,7 @@
         <v>1100</v>
       </c>
       <c r="C20" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G20">
         <f>B22/B20</f>
@@ -44682,10 +44574,10 @@
     </row>
     <row r="21" spans="1:9">
       <c r="B21" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G21" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -44693,7 +44585,7 @@
         <v>793</v>
       </c>
       <c r="C22" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="G22">
         <f>1/G20</f>
@@ -44715,15 +44607,15 @@
   <sheetData>
     <row r="2" spans="2:11">
       <c r="B2" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="2:11">
       <c r="J3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="K3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="2:11">
@@ -44771,39 +44663,39 @@
     </row>
     <row r="18" spans="2:14">
       <c r="B18" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" spans="2:14">
       <c r="B19" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="21" spans="2:14">
       <c r="I21" s="19" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23" spans="2:14">
       <c r="J23" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="K23" t="s">
+        <v>104</v>
+      </c>
+      <c r="L23" t="s">
+        <v>105</v>
+      </c>
+      <c r="M23" t="s">
         <v>106</v>
       </c>
-      <c r="L23" t="s">
+      <c r="N23" t="s">
         <v>107</v>
-      </c>
-      <c r="M23" t="s">
-        <v>108</v>
-      </c>
-      <c r="N23" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="24" spans="2:14">
       <c r="J24" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K24">
         <v>0.79</v>
@@ -44823,7 +44715,7 @@
     </row>
     <row r="25" spans="2:14">
       <c r="J25" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="K25">
         <v>0.79</v>
@@ -44835,7 +44727,7 @@
     </row>
     <row r="26" spans="2:14">
       <c r="J26" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K26">
         <v>0.71699999999999997</v>
@@ -44847,7 +44739,7 @@
     </row>
     <row r="27" spans="2:14">
       <c r="J27" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="K27">
         <v>0.63900000000000001</v>
@@ -44859,12 +44751,12 @@
     </row>
     <row r="28" spans="2:14">
       <c r="J28" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="29" spans="2:14">
       <c r="J29" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="K29">
         <v>0.70299999999999996</v>
@@ -44876,7 +44768,7 @@
     </row>
     <row r="30" spans="2:14">
       <c r="J30" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K30">
         <v>0.63400000000000001</v>
@@ -44888,7 +44780,7 @@
     </row>
     <row r="31" spans="2:14">
       <c r="J31" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="K31">
         <v>0.57599999999999996</v>
@@ -44900,7 +44792,7 @@
     </row>
     <row r="32" spans="2:14">
       <c r="J32" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K32">
         <v>0.57599999999999996</v>
@@ -44923,12 +44815,12 @@
   <sheetData>
     <row r="2" spans="1:2">
       <c r="B2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B3" s="11">
         <v>0.61</v>
@@ -44936,12 +44828,12 @@
     </row>
     <row r="4" spans="1:2">
       <c r="B4" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B5" s="11">
         <v>0.7</v>
@@ -44949,12 +44841,12 @@
     </row>
     <row r="7" spans="1:2">
       <c r="B7" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B8" s="11">
         <v>0.61</v>
@@ -44962,12 +44854,12 @@
     </row>
     <row r="9" spans="1:2">
       <c r="B9" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B10" s="11">
         <v>0.72</v>
@@ -44975,7 +44867,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B12" s="11">
         <f>AVERAGE(B8,B3)</f>
@@ -44984,7 +44876,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="B13">
         <f>1/B12</f>
@@ -45010,7 +44902,7 @@
   <sheetData>
     <row r="1" spans="1:16">
       <c r="A1" s="24" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B1" s="24"/>
       <c r="C1" s="24"/>
@@ -45030,7 +44922,7 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
@@ -45040,30 +44932,30 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" s="25" t="s">
+        <v>141</v>
+      </c>
+      <c r="B3" s="25" t="s">
+        <v>142</v>
+      </c>
+      <c r="C3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D3" t="s">
         <v>143</v>
       </c>
-      <c r="B3" s="25" t="s">
+      <c r="E3" t="s">
         <v>144</v>
       </c>
-      <c r="C3" t="s">
-        <v>140</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="F3" t="s">
         <v>145</v>
       </c>
-      <c r="E3" t="s">
+      <c r="H3" t="s">
         <v>146</v>
-      </c>
-      <c r="F3" t="s">
-        <v>147</v>
-      </c>
-      <c r="H3" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="26" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B4" s="27">
         <v>0.30299999999999999</v>
@@ -45082,12 +44974,12 @@
         <v>19</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="25" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B5" s="27">
         <f>AVERAGE(0.35,0.305,0.266)</f>
@@ -45098,7 +44990,7 @@
         <v>3.2573289902280131</v>
       </c>
       <c r="D5" s="28" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E5">
         <v>2100</v>
@@ -45109,7 +45001,7 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B7" s="29"/>
       <c r="C7" s="29"/>
@@ -45119,18 +45011,18 @@
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="25" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C8" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="25" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="B9">
         <f>AVERAGE(0.836,0.885,0.905)</f>
@@ -45141,7 +45033,7 @@
         <v>1.1424219345011424</v>
       </c>
       <c r="D9" s="28" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E9">
         <v>2600</v>
@@ -45152,7 +45044,7 @@
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="26" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B10">
         <f>B9*(1-AVERAGE(0.1,0.15))</f>
@@ -45164,12 +45056,12 @@
       </c>
       <c r="D10" s="28"/>
       <c r="F10" s="28" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="25" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="B11">
         <f>1/C11</f>
@@ -45188,7 +45080,7 @@
     </row>
     <row r="12" spans="1:16">
       <c r="A12" s="25" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B12">
         <f>1/C12</f>
@@ -45205,7 +45097,7 @@
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
@@ -45215,7 +45107,7 @@
     </row>
     <row r="15" spans="1:16">
       <c r="A15" s="25" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B15" s="14">
         <f>(AVERAGE(C4:C5)-AVERAGE(C10:C12))/AVERAGE(C4:C5)</f>
@@ -45231,104 +45123,104 @@
     </row>
     <row r="19" spans="8:8">
       <c r="H19" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="20" spans="8:8">
       <c r="H20" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="33" spans="1:20">
       <c r="A33" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D33" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="34" spans="1:20">
       <c r="A34" t="s">
+        <v>163</v>
+      </c>
+      <c r="B34" t="s">
+        <v>164</v>
+      </c>
+      <c r="D34" t="s">
         <v>165</v>
       </c>
-      <c r="B34" t="s">
+      <c r="E34" t="s">
         <v>166</v>
       </c>
-      <c r="D34" t="s">
+      <c r="F34" t="s">
         <v>167</v>
       </c>
-      <c r="E34" t="s">
+      <c r="G34" t="s">
         <v>168</v>
       </c>
-      <c r="F34" t="s">
+      <c r="H34" t="s">
         <v>169</v>
       </c>
-      <c r="G34" t="s">
+      <c r="I34" t="s">
         <v>170</v>
       </c>
-      <c r="H34" t="s">
+      <c r="J34" t="s">
         <v>171</v>
       </c>
-      <c r="I34" t="s">
+      <c r="M34" t="s">
         <v>172</v>
       </c>
-      <c r="J34" t="s">
+      <c r="P34" t="s">
         <v>173</v>
       </c>
-      <c r="M34" t="s">
+      <c r="S34" t="s">
         <v>174</v>
       </c>
-      <c r="P34" t="s">
+      <c r="T34" t="s">
         <v>175</v>
-      </c>
-      <c r="S34" t="s">
-        <v>176</v>
-      </c>
-      <c r="T34" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="35" spans="1:20">
       <c r="A35" t="s">
+        <v>176</v>
+      </c>
+      <c r="B35" t="s">
+        <v>177</v>
+      </c>
+      <c r="C35" t="s">
         <v>178</v>
       </c>
-      <c r="B35" t="s">
+      <c r="J35" t="s">
         <v>179</v>
       </c>
-      <c r="C35" t="s">
+      <c r="K35" t="s">
         <v>180</v>
       </c>
-      <c r="J35" t="s">
+      <c r="L35" t="s">
         <v>181</v>
       </c>
-      <c r="K35" t="s">
-        <v>182</v>
-      </c>
-      <c r="L35" t="s">
-        <v>183</v>
-      </c>
       <c r="M35" t="s">
+        <v>179</v>
+      </c>
+      <c r="N35" t="s">
+        <v>180</v>
+      </c>
+      <c r="O35" t="s">
         <v>181</v>
       </c>
-      <c r="N35" t="s">
-        <v>182</v>
-      </c>
-      <c r="O35" t="s">
-        <v>183</v>
-      </c>
       <c r="P35" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>180</v>
+      </c>
+      <c r="R35" t="s">
         <v>181</v>
-      </c>
-      <c r="Q35" t="s">
-        <v>182</v>
-      </c>
-      <c r="R35" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="36" spans="1:20">
       <c r="A36" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B36" s="18">
         <f>AVERAGE(S36:S37)</f>
@@ -45439,7 +45331,7 @@
     </row>
     <row r="38" spans="1:20">
       <c r="A38" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B38" s="18">
         <f>AVERAGE(S38:S40)</f>
@@ -45591,7 +45483,7 @@
     </row>
     <row r="41" spans="1:20">
       <c r="A41" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B41" s="18">
         <f>AVERAGE(S41:S43)</f>
@@ -45723,17 +45615,17 @@
   <sheetData>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B4">
         <v>0.65200000000000002</v>
@@ -45742,7 +45634,7 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="B5">
         <v>0.13650000000000001</v>
@@ -45751,7 +45643,7 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="B6">
         <v>0.20050000000000001</v>
@@ -45760,7 +45652,7 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B7" s="17">
         <v>1.0999999999999999E-2</v>
@@ -45768,17 +45660,17 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="B11" s="11">
         <v>0.9</v>
@@ -45786,7 +45678,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="B12" s="11">
         <v>0.85</v>
@@ -45794,7 +45686,7 @@
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B13" s="11">
         <v>0.1</v>
@@ -45802,18 +45694,18 @@
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B14" s="11">
         <v>0.7</v>
       </c>
       <c r="C14" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B16" s="11">
         <f>B11*B4+B12*B5+B6*B14+B11*B7</f>
@@ -45822,7 +45714,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B17" s="11">
         <f>1/B16</f>
@@ -45831,12 +45723,12 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -45846,7 +45738,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B23" s="11">
         <f>B16*A21</f>
@@ -45855,7 +45747,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B24">
         <f>1/B23</f>
